--- a/excel model/2026-10-03_AGNC_DCF.xlsx
+++ b/excel model/2026-10-03_AGNC_DCF.xlsx
@@ -242,7 +242,7 @@
     <t xml:space="preserve">Current common share price</t>
   </si>
   <si>
-    <t xml:space="preserve">Current market price 8.79 from openbb_yfinance; snapshot timestamp 2026-10-03T22:04:56.257Z; valuation context dated 2026-10-03.</t>
+    <t xml:space="preserve">Current market price 8.79 from openbb_yfinance; snapshot timestamp 2026-10-03T22:41:05.443Z; valuation context dated 2026-10-03.</t>
   </si>
   <si>
     <t xml:space="preserve">Net income available to common</t>
@@ -1005,7 +1005,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-\$* #,##0.00_-;&quot;-$&quot;* #,##0.00_-;_-\$* \-??_-;_-@_-"/>
@@ -1016,6 +1016,7 @@
     <numFmt numFmtId="171" formatCode="\$0.00;[RED]&quot;($&quot;0.00\);\-"/>
     <numFmt numFmtId="172" formatCode="\$#,##0.00;[RED]&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="173" formatCode="0.00\x"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1393,7 +1394,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1511,6 +1512,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3973,10 +3978,10 @@
       <c r="B2" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>40929000000</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>40929</v>
       </c>
       <c r="E2" s="29" t="s">
@@ -3988,28 +3993,28 @@
       <c r="G2" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I2" s="30" t="s">
+      <c r="H2" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N2" s="30" t="s">
+      <c r="N2" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4020,10 +4025,10 @@
       <c r="B3" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>51748000000</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>51748</v>
       </c>
       <c r="E3" s="29" t="s">
@@ -4035,28 +4040,28 @@
       <c r="G3" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H3" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I3" s="30" t="s">
+      <c r="H3" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="M3" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4067,10 +4072,10 @@
       <c r="B4" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>36357000000</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>36357</v>
       </c>
       <c r="E4" s="29" t="s">
@@ -4082,28 +4087,28 @@
       <c r="G4" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="H4" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I4" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4114,10 +4119,10 @@
       <c r="B5" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>43878000000</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>43878</v>
       </c>
       <c r="E5" s="29" t="s">
@@ -4129,28 +4134,28 @@
       <c r="G5" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" s="30" t="s">
+      <c r="H5" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I5" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="L5" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M5" s="30" t="s">
+      <c r="M5" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O5" s="30" t="s">
+      <c r="O5" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4161,10 +4166,10 @@
       <c r="B6" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>7870000000</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>7870</v>
       </c>
       <c r="E6" s="29" t="s">
@@ -4176,28 +4181,28 @@
       <c r="G6" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I6" s="30" t="s">
+      <c r="H6" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M6" s="30" t="s">
+      <c r="M6" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N6" s="30" t="s">
+      <c r="N6" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O6" s="30" t="s">
+      <c r="O6" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4208,10 +4213,10 @@
       <c r="B7" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>10.76</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>10.76</v>
       </c>
       <c r="E7" s="29" t="s">
@@ -4223,28 +4228,28 @@
       <c r="G7" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I7" s="30" t="s">
+      <c r="H7" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M7" s="30" t="s">
+      <c r="M7" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N7" s="30" t="s">
+      <c r="N7" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O7" s="30" t="s">
+      <c r="O7" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4255,10 +4260,10 @@
       <c r="B8" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>9.84</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>9.84</v>
       </c>
       <c r="E8" s="29" t="s">
@@ -4270,28 +4275,28 @@
       <c r="G8" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H8" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="H8" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N8" s="30" t="s">
+      <c r="N8" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O8" s="30" t="s">
+      <c r="O8" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4309,18 +4314,18 @@
       <c r="G9" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="n">
@@ -4336,18 +4341,18 @@
       <c r="G10" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="n">
@@ -4363,18 +4368,18 @@
       <c r="G11" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="n">
@@ -4383,10 +4388,10 @@
       <c r="B12" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="30" t="n">
         <v>1590000000</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>1590</v>
       </c>
       <c r="E12" s="29" t="s">
@@ -4398,28 +4403,28 @@
       <c r="G12" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I12" s="30" t="s">
+      <c r="H12" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I12" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="30" t="s">
+      <c r="K12" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M12" s="30" t="s">
+      <c r="M12" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4430,10 +4435,10 @@
       <c r="B13" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="30" t="n">
         <v>625000000</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>625</v>
       </c>
       <c r="E13" s="29" t="s">
@@ -4445,28 +4450,28 @@
       <c r="G13" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I13" s="30" t="s">
+      <c r="H13" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I13" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="30" t="s">
+      <c r="K13" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L13" s="30" t="s">
+      <c r="L13" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M13" s="30" t="s">
+      <c r="M13" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N13" s="30" t="s">
+      <c r="N13" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O13" s="30" t="s">
+      <c r="O13" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4477,10 +4482,10 @@
       <c r="B14" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="30" t="n">
         <v>965000000</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>965</v>
       </c>
       <c r="E14" s="29" t="s">
@@ -4492,28 +4497,28 @@
       <c r="G14" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H14" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" s="30" t="s">
+      <c r="H14" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="30" t="s">
+      <c r="K14" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L14" s="30" t="s">
+      <c r="L14" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M14" s="30" t="s">
+      <c r="M14" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N14" s="30" t="s">
+      <c r="N14" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O14" s="30" t="s">
+      <c r="O14" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4531,18 +4536,18 @@
       <c r="G15" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="I15" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="n">
@@ -4551,10 +4556,10 @@
       <c r="B16" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>270000</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>0.27</v>
       </c>
       <c r="E16" s="29" t="s">
@@ -4566,28 +4571,28 @@
       <c r="G16" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="30" t="s">
+      <c r="H16" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="J16" s="30" t="s">
+      <c r="J16" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="K16" s="30" t="s">
+      <c r="K16" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="L16" s="30" t="s">
+      <c r="L16" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M16" s="30" t="s">
+      <c r="M16" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N16" s="30" t="s">
+      <c r="N16" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O16" s="30" t="s">
+      <c r="O16" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4605,18 +4610,18 @@
       <c r="G17" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I17" s="30" t="s">
+      <c r="I17" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="n">
@@ -4625,10 +4630,10 @@
       <c r="B18" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="30" t="n">
         <v>74000000</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <v>74</v>
       </c>
       <c r="E18" s="29" t="s">
@@ -4640,28 +4645,28 @@
       <c r="G18" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="30" t="s">
+      <c r="H18" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="J18" s="30" t="s">
+      <c r="J18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L18" s="30" t="s">
+      <c r="L18" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M18" s="30" t="s">
+      <c r="M18" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N18" s="30" t="s">
+      <c r="N18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O18" s="30" t="s">
+      <c r="O18" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4672,10 +4677,10 @@
       <c r="B19" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>-1190000000</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>-1190</v>
       </c>
       <c r="E19" s="29" t="s">
@@ -4687,28 +4692,28 @@
       <c r="G19" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="30" t="s">
+      <c r="H19" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="30" t="s">
+      <c r="J19" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="30" t="s">
+      <c r="K19" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L19" s="30" t="s">
+      <c r="L19" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M19" s="30" t="s">
+      <c r="M19" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N19" s="30" t="s">
+      <c r="N19" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O19" s="30" t="s">
+      <c r="O19" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4719,10 +4724,10 @@
       <c r="B20" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <v>105000000</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>105</v>
       </c>
       <c r="E20" s="29" t="s">
@@ -4734,28 +4739,28 @@
       <c r="G20" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="30" t="s">
+      <c r="H20" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="K20" s="30" t="s">
+      <c r="K20" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L20" s="30" t="s">
+      <c r="L20" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M20" s="30" t="s">
+      <c r="M20" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N20" s="30" t="s">
+      <c r="N20" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O20" s="30" t="s">
+      <c r="O20" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4773,18 +4778,18 @@
       <c r="G21" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H21" s="30" t="s">
+      <c r="H21" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I21" s="30" t="s">
+      <c r="I21" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="n">
@@ -4793,10 +4798,10 @@
       <c r="B22" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="30" t="n">
         <v>-973000000</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="30" t="n">
         <v>-973</v>
       </c>
       <c r="E22" s="29" t="s">
@@ -4808,28 +4813,28 @@
       <c r="G22" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="30" t="s">
+      <c r="H22" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="J22" s="30" t="s">
+      <c r="J22" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="K22" s="30" t="s">
+      <c r="K22" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L22" s="30" t="s">
+      <c r="L22" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M22" s="30" t="s">
+      <c r="M22" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N22" s="30" t="s">
+      <c r="N22" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O22" s="30" t="s">
+      <c r="O22" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4847,18 +4852,18 @@
       <c r="G23" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H23" s="30" t="s">
+      <c r="H23" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I23" s="30" t="s">
+      <c r="I23" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="n">
@@ -4874,18 +4879,18 @@
       <c r="G24" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="H24" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I24" s="30" t="s">
+      <c r="I24" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="n">
@@ -4894,10 +4899,10 @@
       <c r="B25" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <v>1.44</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <v>1.44</v>
       </c>
       <c r="E25" s="29" t="s">
@@ -4909,28 +4914,28 @@
       <c r="G25" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H25" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="30" t="s">
+      <c r="H25" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="J25" s="30" t="s">
+      <c r="J25" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L25" s="30" t="s">
+      <c r="L25" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M25" s="30" t="s">
+      <c r="M25" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N25" s="30" t="s">
+      <c r="N25" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O25" s="30" t="s">
+      <c r="O25" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4941,10 +4946,10 @@
       <c r="B26" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <v>49195000000</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="30" t="n">
         <v>49195</v>
       </c>
       <c r="E26" s="29" t="s">
@@ -4956,28 +4961,28 @@
       <c r="G26" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H26" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="30" t="s">
+      <c r="H26" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="J26" s="30" t="s">
+      <c r="J26" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L26" s="30" t="s">
+      <c r="L26" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M26" s="30" t="s">
+      <c r="M26" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N26" s="30" t="s">
+      <c r="N26" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O26" s="30" t="s">
+      <c r="O26" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4988,10 +4993,10 @@
       <c r="B27" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="30" t="n">
         <v>20631000000</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <v>20631</v>
       </c>
       <c r="E27" s="29" t="s">
@@ -5003,28 +5008,28 @@
       <c r="G27" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H27" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="30" t="s">
+      <c r="H27" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="J27" s="30" t="s">
+      <c r="J27" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="K27" s="30" t="s">
+      <c r="K27" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L27" s="30" t="s">
+      <c r="L27" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M27" s="30" t="s">
+      <c r="M27" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N27" s="30" t="s">
+      <c r="N27" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O27" s="30" t="s">
+      <c r="O27" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5035,10 +5040,10 @@
       <c r="B28" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="30" t="n">
         <v>61028000000</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <v>61028</v>
       </c>
       <c r="E28" s="29" t="s">
@@ -5050,28 +5055,28 @@
       <c r="G28" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="30" t="s">
+      <c r="H28" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="J28" s="30" t="s">
+      <c r="J28" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="K28" s="30" t="s">
+      <c r="K28" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L28" s="30" t="s">
+      <c r="L28" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M28" s="30" t="s">
+      <c r="M28" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N28" s="30" t="s">
+      <c r="N28" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O28" s="30" t="s">
+      <c r="O28" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5082,10 +5087,10 @@
       <c r="B29" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="30" t="n">
         <v>41363000000</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="30" t="n">
         <v>41363</v>
       </c>
       <c r="E29" s="29" t="s">
@@ -5097,28 +5102,28 @@
       <c r="G29" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H29" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" s="30" t="s">
+      <c r="H29" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="J29" s="30" t="s">
+      <c r="J29" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="K29" s="30" t="s">
+      <c r="K29" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L29" s="30" t="s">
+      <c r="L29" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M29" s="30" t="s">
+      <c r="M29" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N29" s="30" t="s">
+      <c r="N29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O29" s="30" t="s">
+      <c r="O29" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5129,10 +5134,10 @@
       <c r="B30" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="30" t="n">
         <v>61994000000</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <v>61994</v>
       </c>
       <c r="E30" s="29" t="s">
@@ -5144,28 +5149,28 @@
       <c r="G30" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H30" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="30" t="s">
+      <c r="H30" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="J30" s="30" t="s">
+      <c r="J30" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="K30" s="30" t="s">
+      <c r="K30" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L30" s="30" t="s">
+      <c r="L30" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M30" s="30" t="s">
+      <c r="M30" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N30" s="30" t="s">
+      <c r="N30" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O30" s="30" t="s">
+      <c r="O30" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5176,10 +5181,10 @@
       <c r="B31" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <v>8475000000</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <v>8475</v>
       </c>
       <c r="E31" s="29" t="s">
@@ -5191,28 +5196,28 @@
       <c r="G31" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="30" t="s">
+      <c r="H31" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="J31" s="30" t="s">
+      <c r="J31" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="K31" s="30" t="s">
+      <c r="K31" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L31" s="30" t="s">
+      <c r="L31" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M31" s="30" t="s">
+      <c r="M31" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N31" s="30" t="s">
+      <c r="N31" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O31" s="30" t="s">
+      <c r="O31" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5223,10 +5228,10 @@
       <c r="B32" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="30" t="n">
         <v>7.8</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="30" t="n">
         <v>7.8</v>
       </c>
       <c r="E32" s="29" t="s">
@@ -5238,28 +5243,28 @@
       <c r="G32" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I32" s="30" t="s">
+      <c r="H32" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="J32" s="30" t="s">
+      <c r="J32" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="30" t="s">
+      <c r="K32" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L32" s="30" t="s">
+      <c r="L32" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M32" s="30" t="s">
+      <c r="M32" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N32" s="30" t="s">
+      <c r="N32" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O32" s="30" t="s">
+      <c r="O32" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5270,10 +5275,10 @@
       <c r="B33" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="30" t="n">
         <v>7.4</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="30" t="n">
         <v>7.4</v>
       </c>
       <c r="E33" s="29" t="s">
@@ -5285,28 +5290,28 @@
       <c r="G33" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="30" t="s">
+      <c r="H33" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I33" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="J33" s="30" t="s">
+      <c r="J33" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="K33" s="30" t="s">
+      <c r="K33" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L33" s="30" t="s">
+      <c r="L33" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M33" s="30" t="s">
+      <c r="M33" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N33" s="30" t="s">
+      <c r="N33" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O33" s="30" t="s">
+      <c r="O33" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5317,10 +5322,10 @@
       <c r="B34" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="30" t="n">
         <v>-0.284</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="30" t="n">
         <v>-28.4</v>
       </c>
       <c r="E34" s="29" t="s">
@@ -5332,28 +5337,28 @@
       <c r="G34" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H34" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I34" s="30" t="s">
+      <c r="H34" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="J34" s="30" t="s">
+      <c r="J34" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K34" s="30" t="s">
+      <c r="K34" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L34" s="30" t="s">
+      <c r="L34" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M34" s="30" t="s">
+      <c r="M34" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N34" s="30" t="s">
+      <c r="N34" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O34" s="30" t="s">
+      <c r="O34" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5367,7 +5372,7 @@
       <c r="C35" s="29" t="n">
         <v>0.0012</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="30" t="n">
         <v>0.12</v>
       </c>
       <c r="E35" s="29" t="s">
@@ -5379,28 +5384,28 @@
       <c r="G35" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H35" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" s="30" t="s">
+      <c r="H35" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="J35" s="30" t="s">
+      <c r="J35" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K35" s="30" t="s">
+      <c r="K35" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L35" s="30" t="s">
+      <c r="L35" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M35" s="30" t="s">
+      <c r="M35" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N35" s="30" t="s">
+      <c r="N35" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O35" s="30" t="s">
+      <c r="O35" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5411,10 +5416,10 @@
       <c r="B36" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="30" t="n">
         <v>0.03</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="30" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="29" t="s">
@@ -5426,28 +5431,28 @@
       <c r="G36" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I36" s="30" t="s">
+      <c r="H36" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I36" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="J36" s="30" t="s">
+      <c r="J36" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="K36" s="30" t="s">
+      <c r="K36" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L36" s="30" t="s">
+      <c r="L36" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M36" s="30" t="s">
+      <c r="M36" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N36" s="30" t="s">
+      <c r="N36" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O36" s="30" t="s">
+      <c r="O36" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5461,7 +5466,7 @@
       <c r="C37" s="29" t="n">
         <v>0.0027</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="30" t="n">
         <v>0.27</v>
       </c>
       <c r="E37" s="29" t="s">
@@ -5473,28 +5478,28 @@
       <c r="G37" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H37" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I37" s="30" t="s">
+      <c r="H37" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I37" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="J37" s="30" t="s">
+      <c r="J37" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K37" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L37" s="30" t="s">
+      <c r="L37" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M37" s="30" t="s">
+      <c r="M37" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N37" s="30" t="s">
+      <c r="N37" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O37" s="30" t="s">
+      <c r="O37" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5505,10 +5510,10 @@
       <c r="B38" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="30" t="n">
         <v>0.0273</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="30" t="n">
         <v>2.73</v>
       </c>
       <c r="E38" s="29" t="s">
@@ -5520,28 +5525,28 @@
       <c r="G38" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" s="30" t="s">
+      <c r="H38" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="J38" s="30" t="s">
+      <c r="J38" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="K38" s="30" t="s">
+      <c r="K38" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L38" s="30" t="s">
+      <c r="L38" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M38" s="30" t="s">
+      <c r="M38" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N38" s="30" t="s">
+      <c r="N38" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O38" s="30" t="s">
+      <c r="O38" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5552,10 +5557,10 @@
       <c r="B39" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="30" t="n">
         <v>49334000000</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="30" t="n">
         <v>49334</v>
       </c>
       <c r="E39" s="29" t="s">
@@ -5567,28 +5572,28 @@
       <c r="G39" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I39" s="30" t="s">
+      <c r="H39" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I39" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="J39" s="30" t="s">
+      <c r="J39" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="K39" s="30" t="s">
+      <c r="K39" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L39" s="30" t="s">
+      <c r="L39" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M39" s="30" t="s">
+      <c r="M39" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N39" s="30" t="s">
+      <c r="N39" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O39" s="30" t="s">
+      <c r="O39" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5599,10 +5604,10 @@
       <c r="B40" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="30" t="n">
         <v>80</v>
       </c>
       <c r="E40" s="29" t="s">
@@ -5614,28 +5619,28 @@
       <c r="G40" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H40" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="30" t="s">
+      <c r="H40" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I40" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="J40" s="30" t="s">
+      <c r="J40" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="K40" s="30" t="s">
+      <c r="K40" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L40" s="30" t="s">
+      <c r="L40" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M40" s="30" t="s">
+      <c r="M40" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N40" s="30" t="s">
+      <c r="N40" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O40" s="30" t="s">
+      <c r="O40" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5646,10 +5651,10 @@
       <c r="B41" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="30" t="n">
         <v>-0.0135</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="30" t="n">
         <v>-1.35</v>
       </c>
       <c r="E41" s="29" t="s">
@@ -5661,28 +5666,28 @@
       <c r="G41" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I41" s="30" t="s">
+      <c r="H41" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I41" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="J41" s="30" t="s">
+      <c r="J41" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="K41" s="30" t="s">
+      <c r="K41" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L41" s="30" t="s">
+      <c r="L41" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="M41" s="30" t="s">
+      <c r="M41" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N41" s="30" t="s">
+      <c r="N41" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O41" s="30" t="s">
+      <c r="O41" s="31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5693,10 +5698,10 @@
       <c r="B42" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="30" t="n">
         <v>54868000000</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="30" t="n">
         <v>54868</v>
       </c>
       <c r="E42" s="29" t="s">
@@ -5708,28 +5713,28 @@
       <c r="G42" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I42" s="30" t="s">
+      <c r="H42" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="J42" s="30" t="s">
+      <c r="J42" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="K42" s="30" t="s">
+      <c r="K42" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L42" s="30" t="s">
+      <c r="L42" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M42" s="30" t="s">
+      <c r="M42" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N42" s="30" t="s">
+      <c r="N42" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O42" s="30" t="s">
+      <c r="O42" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5740,10 +5745,10 @@
       <c r="B43" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="30" t="n">
         <v>71596000000</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="30" t="n">
         <v>71596</v>
       </c>
       <c r="E43" s="29" t="s">
@@ -5755,28 +5760,28 @@
       <c r="G43" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H43" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I43" s="30" t="s">
+      <c r="H43" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="J43" s="30" t="s">
+      <c r="J43" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="30" t="s">
+      <c r="K43" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L43" s="30" t="s">
+      <c r="L43" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M43" s="30" t="s">
+      <c r="M43" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N43" s="30" t="s">
+      <c r="N43" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O43" s="30" t="s">
+      <c r="O43" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5787,10 +5792,10 @@
       <c r="B44" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="30" t="n">
         <v>50506000000</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="30" t="n">
         <v>50506</v>
       </c>
       <c r="E44" s="29" t="s">
@@ -5802,28 +5807,28 @@
       <c r="G44" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I44" s="30" t="s">
+      <c r="H44" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J44" s="30" t="s">
+      <c r="J44" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="K44" s="30" t="s">
+      <c r="K44" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L44" s="30" t="s">
+      <c r="L44" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M44" s="30" t="s">
+      <c r="M44" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N44" s="30" t="s">
+      <c r="N44" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O44" s="30" t="s">
+      <c r="O44" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5834,10 +5839,10 @@
       <c r="B45" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="30" t="n">
         <v>63339000000</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="30" t="n">
         <v>63339</v>
       </c>
       <c r="E45" s="29" t="s">
@@ -5849,28 +5854,28 @@
       <c r="G45" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H45" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I45" s="30" t="s">
+      <c r="H45" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I45" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="J45" s="30" t="s">
+      <c r="J45" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="30" t="s">
+      <c r="K45" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L45" s="30" t="s">
+      <c r="L45" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M45" s="30" t="s">
+      <c r="M45" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N45" s="30" t="s">
+      <c r="N45" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O45" s="30" t="s">
+      <c r="O45" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5881,10 +5886,10 @@
       <c r="B46" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="30" t="n">
         <v>8257000000</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="30" t="n">
         <v>8257</v>
       </c>
       <c r="E46" s="29" t="s">
@@ -5896,28 +5901,28 @@
       <c r="G46" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H46" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I46" s="30" t="s">
+      <c r="H46" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I46" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J46" s="30" t="s">
+      <c r="J46" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="K46" s="30" t="s">
+      <c r="K46" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L46" s="30" t="s">
+      <c r="L46" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M46" s="30" t="s">
+      <c r="M46" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N46" s="30" t="s">
+      <c r="N46" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O46" s="30" t="s">
+      <c r="O46" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5928,10 +5933,10 @@
       <c r="B47" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="30" t="n">
         <v>9.46</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="30" t="n">
         <v>9.46</v>
       </c>
       <c r="E47" s="29" t="s">
@@ -5943,28 +5948,28 @@
       <c r="G47" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H47" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I47" s="30" t="s">
+      <c r="H47" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I47" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J47" s="30" t="s">
+      <c r="J47" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="K47" s="30" t="s">
+      <c r="K47" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L47" s="30" t="s">
+      <c r="L47" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M47" s="30" t="s">
+      <c r="M47" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N47" s="30" t="s">
+      <c r="N47" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O47" s="30" t="s">
+      <c r="O47" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5975,10 +5980,10 @@
       <c r="B48" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="30" t="n">
         <v>8.7</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="30" t="n">
         <v>8.7</v>
       </c>
       <c r="E48" s="29" t="s">
@@ -5990,28 +5995,28 @@
       <c r="G48" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H48" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I48" s="30" t="s">
+      <c r="H48" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I48" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="J48" s="30" t="s">
+      <c r="J48" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="K48" s="30" t="s">
+      <c r="K48" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L48" s="30" t="s">
+      <c r="L48" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M48" s="30" t="s">
+      <c r="M48" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N48" s="30" t="s">
+      <c r="N48" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O48" s="30" t="s">
+      <c r="O48" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6022,10 +6027,10 @@
       <c r="B49" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="30" t="n">
         <v>694300000</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="30" t="n">
         <v>694.3</v>
       </c>
       <c r="E49" s="29" t="s">
@@ -6037,28 +6042,28 @@
       <c r="G49" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H49" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I49" s="30" t="s">
+      <c r="H49" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="J49" s="30" t="s">
+      <c r="J49" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="K49" s="30" t="s">
+      <c r="K49" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="L49" s="30" t="s">
+      <c r="L49" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M49" s="30" t="s">
+      <c r="M49" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N49" s="30" t="s">
+      <c r="N49" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O49" s="30" t="s">
+      <c r="O49" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6069,10 +6074,10 @@
       <c r="B50" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="30" t="n">
         <v>1634000000</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="30" t="n">
         <v>1634</v>
       </c>
       <c r="E50" s="29" t="s">
@@ -6084,28 +6089,28 @@
       <c r="G50" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H50" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I50" s="30" t="s">
+      <c r="H50" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I50" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="J50" s="30" t="s">
+      <c r="J50" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="K50" s="30" t="s">
+      <c r="K50" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="L50" s="30" t="s">
+      <c r="L50" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M50" s="30" t="s">
+      <c r="M50" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N50" s="30" t="s">
+      <c r="N50" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O50" s="30" t="s">
+      <c r="O50" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6116,10 +6121,10 @@
       <c r="B51" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="30" t="n">
         <v>1688000000</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="30" t="n">
         <v>1688</v>
       </c>
       <c r="E51" s="29" t="s">
@@ -6131,28 +6136,28 @@
       <c r="G51" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I51" s="30" t="s">
+      <c r="H51" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I51" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="J51" s="30" t="s">
+      <c r="J51" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="K51" s="30" t="s">
+      <c r="K51" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="L51" s="30" t="s">
+      <c r="L51" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M51" s="30" t="s">
+      <c r="M51" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N51" s="30" t="s">
+      <c r="N51" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O51" s="30" t="s">
+      <c r="O51" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6163,10 +6168,10 @@
       <c r="B52" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="30" t="n">
         <v>2041000000</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="30" t="n">
         <v>2041</v>
       </c>
       <c r="E52" s="29" t="s">
@@ -6178,28 +6183,28 @@
       <c r="G52" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I52" s="30" t="s">
+      <c r="H52" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I52" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="J52" s="30" t="s">
+      <c r="J52" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="K52" s="30" t="s">
+      <c r="K52" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L52" s="30" t="s">
+      <c r="L52" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M52" s="30" t="s">
+      <c r="M52" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N52" s="30" t="s">
+      <c r="N52" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O52" s="30" t="s">
+      <c r="O52" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6210,10 +6215,10 @@
       <c r="B53" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="30" t="n">
         <v>2287000000</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="30" t="n">
         <v>2287</v>
       </c>
       <c r="E53" s="29" t="s">
@@ -6225,28 +6230,28 @@
       <c r="G53" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H53" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I53" s="30" t="s">
+      <c r="H53" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I53" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="J53" s="30" t="s">
+      <c r="J53" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K53" s="30" t="s">
+      <c r="K53" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L53" s="30" t="s">
+      <c r="L53" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M53" s="30" t="s">
+      <c r="M53" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N53" s="30" t="s">
+      <c r="N53" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O53" s="30" t="s">
+      <c r="O53" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6257,10 +6262,10 @@
       <c r="B54" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="30" t="n">
         <v>-246000000</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="30" t="n">
         <v>-246</v>
       </c>
       <c r="E54" s="29" t="s">
@@ -6272,28 +6277,28 @@
       <c r="G54" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H54" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I54" s="30" t="s">
+      <c r="H54" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="J54" s="30" t="s">
+      <c r="J54" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K54" s="30" t="s">
+      <c r="K54" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L54" s="30" t="s">
+      <c r="L54" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M54" s="30" t="s">
+      <c r="M54" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N54" s="30" t="s">
+      <c r="N54" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O54" s="30" t="s">
+      <c r="O54" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6304,10 +6309,10 @@
       <c r="B55" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="30" t="n">
         <v>4110000</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="30" t="n">
         <v>4.11</v>
       </c>
       <c r="E55" s="29" t="s">
@@ -6319,28 +6324,28 @@
       <c r="G55" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H55" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I55" s="30" t="s">
+      <c r="H55" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J55" s="30" t="s">
+      <c r="J55" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="K55" s="30" t="s">
+      <c r="K55" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="L55" s="30" t="s">
+      <c r="L55" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M55" s="30" t="s">
+      <c r="M55" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="N55" s="30" t="s">
+      <c r="N55" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="O55" s="30" t="s">
+      <c r="O55" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6351,10 +6356,10 @@
       <c r="B56" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="30" t="n">
         <v>578000000</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="30" t="n">
         <v>578</v>
       </c>
       <c r="E56" s="29" t="s">
@@ -6366,28 +6371,28 @@
       <c r="G56" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H56" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I56" s="30" t="s">
+      <c r="H56" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I56" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="J56" s="30" t="s">
+      <c r="J56" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="K56" s="30" t="s">
+      <c r="K56" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="L56" s="30" t="s">
+      <c r="L56" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M56" s="30" t="s">
+      <c r="M56" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N56" s="30" t="s">
+      <c r="N56" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O56" s="30" t="s">
+      <c r="O56" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6398,10 +6403,10 @@
       <c r="B57" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="30" t="n">
         <v>497000000</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="30" t="n">
         <v>497</v>
       </c>
       <c r="E57" s="29" t="s">
@@ -6413,28 +6418,28 @@
       <c r="G57" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H57" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I57" s="30" t="s">
+      <c r="H57" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="J57" s="30" t="s">
+      <c r="J57" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="K57" s="30" t="s">
+      <c r="K57" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L57" s="30" t="s">
+      <c r="L57" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M57" s="30" t="s">
+      <c r="M57" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N57" s="30" t="s">
+      <c r="N57" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O57" s="30" t="s">
+      <c r="O57" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6445,10 +6450,10 @@
       <c r="B58" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="30" t="n">
         <v>96000000</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="30" t="n">
         <v>96</v>
       </c>
       <c r="E58" s="29" t="s">
@@ -6460,28 +6465,28 @@
       <c r="G58" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H58" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I58" s="30" t="s">
+      <c r="H58" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I58" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="J58" s="30" t="s">
+      <c r="J58" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="K58" s="30" t="s">
+      <c r="K58" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L58" s="30" t="s">
+      <c r="L58" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M58" s="30" t="s">
+      <c r="M58" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N58" s="30" t="s">
+      <c r="N58" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O58" s="30" t="s">
+      <c r="O58" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6492,10 +6497,10 @@
       <c r="B59" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="30" t="n">
         <v>155000000</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="30" t="n">
         <v>155</v>
       </c>
       <c r="E59" s="29" t="s">
@@ -6507,28 +6512,28 @@
       <c r="G59" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H59" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I59" s="30" t="s">
+      <c r="H59" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I59" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J59" s="30" t="s">
+      <c r="J59" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="K59" s="30" t="s">
+      <c r="K59" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L59" s="30" t="s">
+      <c r="L59" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M59" s="30" t="s">
+      <c r="M59" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N59" s="30" t="s">
+      <c r="N59" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O59" s="30" t="s">
+      <c r="O59" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6539,10 +6544,10 @@
       <c r="B60" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="30" t="n">
         <v>123000000</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="30" t="n">
         <v>123</v>
       </c>
       <c r="E60" s="29" t="s">
@@ -6554,28 +6559,28 @@
       <c r="G60" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H60" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I60" s="30" t="s">
+      <c r="H60" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I60" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="J60" s="30" t="s">
+      <c r="J60" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="K60" s="30" t="s">
+      <c r="K60" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L60" s="30" t="s">
+      <c r="L60" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M60" s="30" t="s">
+      <c r="M60" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N60" s="30" t="s">
+      <c r="N60" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O60" s="30" t="s">
+      <c r="O60" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6586,10 +6591,10 @@
       <c r="B61" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="30" t="n">
         <v>32000000</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="30" t="n">
         <v>32</v>
       </c>
       <c r="E61" s="29" t="s">
@@ -6601,28 +6606,28 @@
       <c r="G61" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H61" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I61" s="30" t="s">
+      <c r="H61" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I61" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="J61" s="30" t="s">
+      <c r="J61" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="K61" s="30" t="s">
+      <c r="K61" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L61" s="30" t="s">
+      <c r="L61" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M61" s="30" t="s">
+      <c r="M61" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N61" s="30" t="s">
+      <c r="N61" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O61" s="30" t="s">
+      <c r="O61" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6633,10 +6638,10 @@
       <c r="B62" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="30" t="n">
         <v>155000000</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="30" t="n">
         <v>155</v>
       </c>
       <c r="E62" s="29" t="s">
@@ -6648,28 +6653,28 @@
       <c r="G62" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H62" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I62" s="30" t="s">
+      <c r="H62" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I62" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="J62" s="30" t="s">
+      <c r="J62" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="K62" s="30" t="s">
+      <c r="K62" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L62" s="30" t="s">
+      <c r="L62" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M62" s="30" t="s">
+      <c r="M62" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N62" s="30" t="s">
+      <c r="N62" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O62" s="30" t="s">
+      <c r="O62" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6687,18 +6692,18 @@
       <c r="G63" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H63" s="30" t="s">
+      <c r="H63" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I63" s="30" t="s">
+      <c r="I63" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="J63" s="30"/>
-      <c r="K63" s="30"/>
-      <c r="L63" s="30"/>
-      <c r="M63" s="30"/>
-      <c r="N63" s="30"/>
-      <c r="O63" s="30"/>
+      <c r="J63" s="31"/>
+      <c r="K63" s="31"/>
+      <c r="L63" s="31"/>
+      <c r="M63" s="31"/>
+      <c r="N63" s="31"/>
+      <c r="O63" s="31"/>
     </row>
     <row r="64" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="29" t="n">
@@ -6707,10 +6712,10 @@
       <c r="B64" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="30" t="n">
         <v>187000000</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="30" t="n">
         <v>187</v>
       </c>
       <c r="E64" s="29" t="s">
@@ -6722,28 +6727,28 @@
       <c r="G64" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H64" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I64" s="30" t="s">
+      <c r="H64" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I64" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="J64" s="30" t="s">
+      <c r="J64" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="K64" s="30" t="s">
+      <c r="K64" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L64" s="30" t="s">
+      <c r="L64" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M64" s="30" t="s">
+      <c r="M64" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N64" s="30" t="s">
+      <c r="N64" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O64" s="30" t="s">
+      <c r="O64" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6754,10 +6759,10 @@
       <c r="B65" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="30" t="n">
         <v>1.44</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="30" t="n">
         <v>1.44</v>
       </c>
       <c r="E65" s="29" t="s">
@@ -6769,28 +6774,28 @@
       <c r="G65" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H65" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I65" s="30" t="s">
+      <c r="H65" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I65" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="J65" s="30" t="s">
+      <c r="J65" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="K65" s="30" t="s">
+      <c r="K65" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L65" s="30" t="s">
+      <c r="L65" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M65" s="30" t="s">
+      <c r="M65" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N65" s="30" t="s">
+      <c r="N65" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O65" s="30" t="s">
+      <c r="O65" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6801,10 +6806,10 @@
       <c r="B66" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="30" t="n">
         <v>52262000000</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="30" t="n">
         <v>52262</v>
       </c>
       <c r="E66" s="29" t="s">
@@ -6816,28 +6821,28 @@
       <c r="G66" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H66" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I66" s="30" t="s">
+      <c r="H66" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I66" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="J66" s="30" t="s">
+      <c r="J66" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K66" s="30" t="s">
+      <c r="K66" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L66" s="30" t="s">
+      <c r="L66" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M66" s="30" t="s">
+      <c r="M66" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N66" s="30" t="s">
+      <c r="N66" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O66" s="30" t="s">
+      <c r="O66" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6848,10 +6853,10 @@
       <c r="B67" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="30" t="n">
         <v>10000000000</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="30" t="n">
         <v>10000</v>
       </c>
       <c r="E67" s="29" t="s">
@@ -6863,28 +6868,28 @@
       <c r="G67" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H67" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I67" s="30" t="s">
+      <c r="H67" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I67" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="J67" s="30" t="s">
+      <c r="J67" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="K67" s="30" t="s">
+      <c r="K67" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L67" s="30" t="s">
+      <c r="L67" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M67" s="30" t="s">
+      <c r="M67" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N67" s="30" t="s">
+      <c r="N67" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O67" s="30" t="s">
+      <c r="O67" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6895,10 +6900,10 @@
       <c r="B68" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="30" t="n">
         <v>63409000000</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="30" t="n">
         <v>63409</v>
       </c>
       <c r="E68" s="29" t="s">
@@ -6910,28 +6915,28 @@
       <c r="G68" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H68" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I68" s="30" t="s">
+      <c r="H68" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I68" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="J68" s="30" t="s">
+      <c r="J68" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="K68" s="30" t="s">
+      <c r="K68" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L68" s="30" t="s">
+      <c r="L68" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M68" s="30" t="s">
+      <c r="M68" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N68" s="30" t="s">
+      <c r="N68" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O68" s="30" t="s">
+      <c r="O68" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6942,10 +6947,10 @@
       <c r="B69" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="30" t="n">
         <v>44027000000</v>
       </c>
-      <c r="D69" s="29" t="n">
+      <c r="D69" s="30" t="n">
         <v>44027</v>
       </c>
       <c r="E69" s="29" t="s">
@@ -6957,28 +6962,28 @@
       <c r="G69" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H69" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I69" s="30" t="s">
+      <c r="H69" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I69" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="J69" s="30" t="s">
+      <c r="J69" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="K69" s="30" t="s">
+      <c r="K69" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L69" s="30" t="s">
+      <c r="L69" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M69" s="30" t="s">
+      <c r="M69" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N69" s="30" t="s">
+      <c r="N69" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O69" s="30" t="s">
+      <c r="O69" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6989,10 +6994,10 @@
       <c r="B70" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="30" t="n">
         <v>54027000000</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="30" t="n">
         <v>54027</v>
       </c>
       <c r="E70" s="29" t="s">
@@ -7004,28 +7009,28 @@
       <c r="G70" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H70" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I70" s="30" t="s">
+      <c r="H70" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I70" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="J70" s="30" t="s">
+      <c r="J70" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="K70" s="30" t="s">
+      <c r="K70" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L70" s="30" t="s">
+      <c r="L70" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M70" s="30" t="s">
+      <c r="M70" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N70" s="30" t="s">
+      <c r="N70" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O70" s="30" t="s">
+      <c r="O70" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7036,10 +7041,10 @@
       <c r="B71" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="30" t="n">
         <v>7817000000</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="30" t="n">
         <v>7817</v>
       </c>
       <c r="E71" s="29" t="s">
@@ -7051,28 +7056,28 @@
       <c r="G71" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H71" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I71" s="30" t="s">
+      <c r="H71" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I71" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="J71" s="30" t="s">
+      <c r="J71" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="K71" s="30" t="s">
+      <c r="K71" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L71" s="30" t="s">
+      <c r="L71" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M71" s="30" t="s">
+      <c r="M71" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N71" s="30" t="s">
+      <c r="N71" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O71" s="30" t="s">
+      <c r="O71" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7083,10 +7088,10 @@
       <c r="B72" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="30" t="n">
         <v>7.4</v>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="30" t="n">
         <v>7.4</v>
       </c>
       <c r="E72" s="29" t="s">
@@ -7098,28 +7103,28 @@
       <c r="G72" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H72" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I72" s="30" t="s">
+      <c r="H72" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I72" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="J72" s="30" t="s">
+      <c r="J72" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K72" s="30" t="s">
+      <c r="K72" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L72" s="30" t="s">
+      <c r="L72" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M72" s="30" t="s">
+      <c r="M72" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N72" s="30" t="s">
+      <c r="N72" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O72" s="30" t="s">
+      <c r="O72" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7130,10 +7135,10 @@
       <c r="B73" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="30" t="n">
         <v>7</v>
       </c>
       <c r="E73" s="29" t="s">
@@ -7145,28 +7150,28 @@
       <c r="G73" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H73" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I73" s="30" t="s">
+      <c r="H73" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I73" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="J73" s="30" t="s">
+      <c r="J73" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="K73" s="30" t="s">
+      <c r="K73" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L73" s="30" t="s">
+      <c r="L73" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M73" s="30" t="s">
+      <c r="M73" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N73" s="30" t="s">
+      <c r="N73" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O73" s="30" t="s">
+      <c r="O73" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7177,10 +7182,10 @@
       <c r="B74" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="30" t="n">
         <v>0.03</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="30" t="n">
         <v>3</v>
       </c>
       <c r="E74" s="29" t="s">
@@ -7192,28 +7197,28 @@
       <c r="G74" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H74" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I74" s="30" t="s">
+      <c r="H74" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I74" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="J74" s="30" t="s">
+      <c r="J74" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K74" s="30" t="s">
+      <c r="K74" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L74" s="30" t="s">
+      <c r="L74" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M74" s="30" t="s">
+      <c r="M74" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N74" s="30" t="s">
+      <c r="N74" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O74" s="30" t="s">
+      <c r="O74" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7227,7 +7232,7 @@
       <c r="C75" s="29" t="n">
         <v>0.0015</v>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="30" t="n">
         <v>0.15</v>
       </c>
       <c r="E75" s="29" t="s">
@@ -7239,28 +7244,28 @@
       <c r="G75" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H75" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I75" s="30" t="s">
+      <c r="H75" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I75" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="J75" s="30" t="s">
+      <c r="J75" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K75" s="30" t="s">
+      <c r="K75" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L75" s="30" t="s">
+      <c r="L75" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M75" s="30" t="s">
+      <c r="M75" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N75" s="30" t="s">
+      <c r="N75" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O75" s="30" t="s">
+      <c r="O75" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7271,10 +7276,10 @@
       <c r="B76" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="30" t="n">
         <v>0.0411</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="30" t="n">
         <v>4.11</v>
       </c>
       <c r="E76" s="29" t="s">
@@ -7286,28 +7291,28 @@
       <c r="G76" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H76" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I76" s="30" t="s">
+      <c r="H76" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I76" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="J76" s="30" t="s">
+      <c r="J76" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="K76" s="30" t="s">
+      <c r="K76" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L76" s="30" t="s">
+      <c r="L76" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M76" s="30" t="s">
+      <c r="M76" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N76" s="30" t="s">
+      <c r="N76" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O76" s="30" t="s">
+      <c r="O76" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7318,10 +7323,10 @@
       <c r="B77" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="30" t="n">
         <v>0.0105</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="30" t="n">
         <v>1.05</v>
       </c>
       <c r="E77" s="29" t="s">
@@ -7333,28 +7338,28 @@
       <c r="G77" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H77" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I77" s="30" t="s">
+      <c r="H77" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I77" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="J77" s="30" t="s">
+      <c r="J77" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="K77" s="30" t="s">
+      <c r="K77" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L77" s="30" t="s">
+      <c r="L77" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M77" s="30" t="s">
+      <c r="M77" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N77" s="30" t="s">
+      <c r="N77" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O77" s="30" t="s">
+      <c r="O77" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7365,10 +7370,10 @@
       <c r="B78" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="C78" s="29" t="n">
+      <c r="C78" s="30" t="n">
         <v>0.0306</v>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="30" t="n">
         <v>3.06</v>
       </c>
       <c r="E78" s="29" t="s">
@@ -7380,28 +7385,28 @@
       <c r="G78" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H78" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I78" s="30" t="s">
+      <c r="H78" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I78" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="J78" s="30" t="s">
+      <c r="J78" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="K78" s="30" t="s">
+      <c r="K78" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L78" s="30" t="s">
+      <c r="L78" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M78" s="30" t="s">
+      <c r="M78" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N78" s="30" t="s">
+      <c r="N78" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O78" s="30" t="s">
+      <c r="O78" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7412,10 +7417,10 @@
       <c r="B79" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C79" s="30" t="n">
         <v>47012000000</v>
       </c>
-      <c r="D79" s="29" t="n">
+      <c r="D79" s="30" t="n">
         <v>47012</v>
       </c>
       <c r="E79" s="29" t="s">
@@ -7427,28 +7432,28 @@
       <c r="G79" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H79" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I79" s="30" t="s">
+      <c r="H79" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I79" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="J79" s="30" t="s">
+      <c r="J79" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="K79" s="30" t="s">
+      <c r="K79" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L79" s="30" t="s">
+      <c r="L79" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M79" s="30" t="s">
+      <c r="M79" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N79" s="30" t="s">
+      <c r="N79" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O79" s="30" t="s">
+      <c r="O79" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7459,10 +7464,10 @@
       <c r="B80" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="C80" s="29" t="n">
+      <c r="C80" s="30" t="n">
         <v>0.87</v>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="30" t="n">
         <v>87</v>
       </c>
       <c r="E80" s="29" t="s">
@@ -7474,28 +7479,28 @@
       <c r="G80" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H80" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I80" s="30" t="s">
+      <c r="H80" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I80" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="J80" s="30" t="s">
+      <c r="J80" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="K80" s="30" t="s">
+      <c r="K80" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L80" s="30" t="s">
+      <c r="L80" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M80" s="30" t="s">
+      <c r="M80" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N80" s="30" t="s">
+      <c r="N80" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O80" s="30" t="s">
+      <c r="O80" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7506,10 +7511,10 @@
       <c r="B81" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="C81" s="29" t="n">
+      <c r="C81" s="30" t="n">
         <v>-0.0462</v>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="30" t="n">
         <v>-4.62</v>
       </c>
       <c r="E81" s="29" t="s">
@@ -7521,28 +7526,28 @@
       <c r="G81" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H81" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I81" s="30" t="s">
+      <c r="H81" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I81" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="J81" s="30" t="s">
+      <c r="J81" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="K81" s="30" t="s">
+      <c r="K81" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L81" s="30" t="s">
+      <c r="L81" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="M81" s="30" t="s">
+      <c r="M81" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N81" s="30" t="s">
+      <c r="N81" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O81" s="30" t="s">
+      <c r="O81" s="31" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7553,10 +7558,10 @@
       <c r="B82" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C82" s="29" t="n">
+      <c r="C82" s="30" t="n">
         <v>66412000000</v>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="30" t="n">
         <v>66412</v>
       </c>
       <c r="E82" s="29" t="s">
@@ -7568,28 +7573,28 @@
       <c r="G82" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H82" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I82" s="30" t="s">
+      <c r="H82" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I82" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="J82" s="30" t="s">
+      <c r="J82" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="K82" s="30" t="s">
+      <c r="K82" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L82" s="30" t="s">
+      <c r="L82" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M82" s="30" t="s">
+      <c r="M82" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N82" s="30" t="s">
+      <c r="N82" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O82" s="30" t="s">
+      <c r="O82" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7600,10 +7605,10 @@
       <c r="B83" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="29" t="n">
+      <c r="C83" s="30" t="n">
         <v>88015000000</v>
       </c>
-      <c r="D83" s="29" t="n">
+      <c r="D83" s="30" t="n">
         <v>88015</v>
       </c>
       <c r="E83" s="29" t="s">
@@ -7615,28 +7620,28 @@
       <c r="G83" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H83" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I83" s="30" t="s">
+      <c r="H83" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I83" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="J83" s="30" t="s">
+      <c r="J83" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="K83" s="30" t="s">
+      <c r="K83" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L83" s="30" t="s">
+      <c r="L83" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M83" s="30" t="s">
+      <c r="M83" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N83" s="30" t="s">
+      <c r="N83" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O83" s="30" t="s">
+      <c r="O83" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7647,10 +7652,10 @@
       <c r="B84" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="C84" s="29" t="n">
+      <c r="C84" s="30" t="n">
         <v>60862000000</v>
       </c>
-      <c r="D84" s="29" t="n">
+      <c r="D84" s="30" t="n">
         <v>60862</v>
       </c>
       <c r="E84" s="29" t="s">
@@ -7662,28 +7667,28 @@
       <c r="G84" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H84" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I84" s="30" t="s">
+      <c r="H84" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I84" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J84" s="30" t="s">
+      <c r="J84" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="K84" s="30" t="s">
+      <c r="K84" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L84" s="30" t="s">
+      <c r="L84" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M84" s="30" t="s">
+      <c r="M84" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N84" s="30" t="s">
+      <c r="N84" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O84" s="30" t="s">
+      <c r="O84" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7694,10 +7699,10 @@
       <c r="B85" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C85" s="29" t="n">
+      <c r="C85" s="30" t="n">
         <v>78253000000</v>
       </c>
-      <c r="D85" s="29" t="n">
+      <c r="D85" s="30" t="n">
         <v>78253</v>
       </c>
       <c r="E85" s="29" t="s">
@@ -7709,28 +7714,28 @@
       <c r="G85" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H85" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I85" s="30" t="s">
+      <c r="H85" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I85" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="J85" s="30" t="s">
+      <c r="J85" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="K85" s="30" t="s">
+      <c r="K85" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L85" s="30" t="s">
+      <c r="L85" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M85" s="30" t="s">
+      <c r="M85" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N85" s="30" t="s">
+      <c r="N85" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O85" s="30" t="s">
+      <c r="O85" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7741,10 +7746,10 @@
       <c r="B86" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="29" t="n">
+      <c r="C86" s="30" t="n">
         <v>9762000000</v>
       </c>
-      <c r="D86" s="29" t="n">
+      <c r="D86" s="30" t="n">
         <v>9762</v>
       </c>
       <c r="E86" s="29" t="s">
@@ -7756,28 +7761,28 @@
       <c r="G86" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H86" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I86" s="30" t="s">
+      <c r="H86" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I86" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J86" s="30" t="s">
+      <c r="J86" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="K86" s="30" t="s">
+      <c r="K86" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L86" s="30" t="s">
+      <c r="L86" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M86" s="30" t="s">
+      <c r="M86" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N86" s="30" t="s">
+      <c r="N86" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O86" s="30" t="s">
+      <c r="O86" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7788,10 +7793,10 @@
       <c r="B87" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="C87" s="29" t="n">
+      <c r="C87" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="D87" s="29" t="n">
+      <c r="D87" s="30" t="n">
         <v>9</v>
       </c>
       <c r="E87" s="29" t="s">
@@ -7803,28 +7808,28 @@
       <c r="G87" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H87" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I87" s="30" t="s">
+      <c r="H87" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I87" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J87" s="30" t="s">
+      <c r="J87" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="K87" s="30" t="s">
+      <c r="K87" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L87" s="30" t="s">
+      <c r="L87" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M87" s="30" t="s">
+      <c r="M87" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N87" s="30" t="s">
+      <c r="N87" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O87" s="30" t="s">
+      <c r="O87" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7835,10 +7840,10 @@
       <c r="B88" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C88" s="29" t="n">
+      <c r="C88" s="30" t="n">
         <v>8.41</v>
       </c>
-      <c r="D88" s="29" t="n">
+      <c r="D88" s="30" t="n">
         <v>8.41</v>
       </c>
       <c r="E88" s="29" t="s">
@@ -7850,28 +7855,28 @@
       <c r="G88" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H88" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I88" s="30" t="s">
+      <c r="H88" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I88" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="J88" s="30" t="s">
+      <c r="J88" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="K88" s="30" t="s">
+      <c r="K88" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L88" s="30" t="s">
+      <c r="L88" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M88" s="30" t="s">
+      <c r="M88" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N88" s="30" t="s">
+      <c r="N88" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O88" s="30" t="s">
+      <c r="O88" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7882,10 +7887,10 @@
       <c r="B89" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C89" s="29" t="n">
+      <c r="C89" s="30" t="n">
         <v>897400000</v>
       </c>
-      <c r="D89" s="29" t="n">
+      <c r="D89" s="30" t="n">
         <v>897.4</v>
       </c>
       <c r="E89" s="29" t="s">
@@ -7897,28 +7902,28 @@
       <c r="G89" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H89" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I89" s="30" t="s">
+      <c r="H89" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I89" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="J89" s="30" t="s">
+      <c r="J89" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="K89" s="30" t="s">
+      <c r="K89" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="L89" s="30" t="s">
+      <c r="L89" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M89" s="30" t="s">
+      <c r="M89" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N89" s="30" t="s">
+      <c r="N89" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O89" s="30" t="s">
+      <c r="O89" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7929,10 +7934,10 @@
       <c r="B90" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="C90" s="29" t="n">
+      <c r="C90" s="30" t="n">
         <v>1634000000</v>
       </c>
-      <c r="D90" s="29" t="n">
+      <c r="D90" s="30" t="n">
         <v>1634</v>
       </c>
       <c r="E90" s="29" t="s">
@@ -7944,28 +7949,28 @@
       <c r="G90" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H90" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I90" s="30" t="s">
+      <c r="H90" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I90" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="J90" s="30" t="s">
+      <c r="J90" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="K90" s="30" t="s">
+      <c r="K90" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="L90" s="30" t="s">
+      <c r="L90" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M90" s="30" t="s">
+      <c r="M90" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N90" s="30" t="s">
+      <c r="N90" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O90" s="30" t="s">
+      <c r="O90" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7976,10 +7981,10 @@
       <c r="B91" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="C91" s="29" t="n">
+      <c r="C91" s="30" t="n">
         <v>1688000000</v>
       </c>
-      <c r="D91" s="29" t="n">
+      <c r="D91" s="30" t="n">
         <v>1688</v>
       </c>
       <c r="E91" s="29" t="s">
@@ -7991,28 +7996,28 @@
       <c r="G91" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H91" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I91" s="30" t="s">
+      <c r="H91" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I91" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="J91" s="30" t="s">
+      <c r="J91" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="K91" s="30" t="s">
+      <c r="K91" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="L91" s="30" t="s">
+      <c r="L91" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M91" s="30" t="s">
+      <c r="M91" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N91" s="30" t="s">
+      <c r="N91" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O91" s="30" t="s">
+      <c r="O91" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8023,10 +8028,10 @@
       <c r="B92" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C92" s="29" t="n">
+      <c r="C92" s="30" t="n">
         <v>2949000000</v>
       </c>
-      <c r="D92" s="29" t="n">
+      <c r="D92" s="30" t="n">
         <v>2949</v>
       </c>
       <c r="E92" s="29" t="s">
@@ -8038,28 +8043,28 @@
       <c r="G92" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H92" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I92" s="30" t="s">
+      <c r="H92" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I92" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="J92" s="30" t="s">
+      <c r="J92" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="K92" s="30" t="s">
+      <c r="K92" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L92" s="30" t="s">
+      <c r="L92" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M92" s="30" t="s">
+      <c r="M92" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N92" s="30" t="s">
+      <c r="N92" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O92" s="30" t="s">
+      <c r="O92" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8070,10 +8075,10 @@
       <c r="B93" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C93" s="29" t="n">
+      <c r="C93" s="30" t="n">
         <v>2931000000</v>
       </c>
-      <c r="D93" s="29" t="n">
+      <c r="D93" s="30" t="n">
         <v>2931</v>
       </c>
       <c r="E93" s="29" t="s">
@@ -8085,28 +8090,28 @@
       <c r="G93" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H93" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I93" s="30" t="s">
+      <c r="H93" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I93" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="J93" s="30" t="s">
+      <c r="J93" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="30" t="s">
+      <c r="K93" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L93" s="30" t="s">
+      <c r="L93" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M93" s="30" t="s">
+      <c r="M93" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N93" s="30" t="s">
+      <c r="N93" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O93" s="30" t="s">
+      <c r="O93" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8117,10 +8122,10 @@
       <c r="B94" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C94" s="29" t="n">
+      <c r="C94" s="30" t="n">
         <v>18000000</v>
       </c>
-      <c r="D94" s="29" t="n">
+      <c r="D94" s="30" t="n">
         <v>18</v>
       </c>
       <c r="E94" s="29" t="s">
@@ -8132,28 +8137,28 @@
       <c r="G94" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H94" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I94" s="30" t="s">
+      <c r="H94" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I94" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="J94" s="30" t="s">
+      <c r="J94" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="30" t="s">
+      <c r="K94" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L94" s="30" t="s">
+      <c r="L94" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M94" s="30" t="s">
+      <c r="M94" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N94" s="30" t="s">
+      <c r="N94" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O94" s="30" t="s">
+      <c r="O94" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8164,10 +8169,10 @@
       <c r="B95" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="C95" s="29" t="n">
+      <c r="C95" s="30" t="n">
         <v>4700000</v>
       </c>
-      <c r="D95" s="29" t="n">
+      <c r="D95" s="30" t="n">
         <v>4.7</v>
       </c>
       <c r="E95" s="29" t="s">
@@ -8179,28 +8184,28 @@
       <c r="G95" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H95" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I95" s="30" t="s">
+      <c r="H95" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I95" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J95" s="30" t="s">
+      <c r="J95" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="K95" s="30" t="s">
+      <c r="K95" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="L95" s="30" t="s">
+      <c r="L95" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M95" s="30" t="s">
+      <c r="M95" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N95" s="30" t="s">
+      <c r="N95" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O95" s="30" t="s">
+      <c r="O95" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8211,10 +8216,10 @@
       <c r="B96" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C96" s="29" t="n">
+      <c r="C96" s="30" t="n">
         <v>1395000000</v>
       </c>
-      <c r="D96" s="29" t="n">
+      <c r="D96" s="30" t="n">
         <v>1395</v>
       </c>
       <c r="E96" s="29" t="s">
@@ -8226,28 +8231,28 @@
       <c r="G96" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H96" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I96" s="30" t="s">
+      <c r="H96" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I96" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="J96" s="30" t="s">
+      <c r="J96" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="K96" s="30" t="s">
+      <c r="K96" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="L96" s="30" t="s">
+      <c r="L96" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M96" s="30" t="s">
+      <c r="M96" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N96" s="30" t="s">
+      <c r="N96" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O96" s="30" t="s">
+      <c r="O96" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8258,10 +8263,10 @@
       <c r="B97" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C97" s="29" t="n">
+      <c r="C97" s="30" t="n">
         <v>955000000</v>
       </c>
-      <c r="D97" s="29" t="n">
+      <c r="D97" s="30" t="n">
         <v>955</v>
       </c>
       <c r="E97" s="29" t="s">
@@ -8273,28 +8278,28 @@
       <c r="G97" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H97" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I97" s="30" t="s">
+      <c r="H97" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I97" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="J97" s="30" t="s">
+      <c r="J97" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="K97" s="30" t="s">
+      <c r="K97" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L97" s="30" t="s">
+      <c r="L97" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M97" s="30" t="s">
+      <c r="M97" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N97" s="30" t="s">
+      <c r="N97" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O97" s="30" t="s">
+      <c r="O97" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8305,10 +8310,10 @@
       <c r="B98" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C98" s="29" t="n">
+      <c r="C98" s="30" t="n">
         <v>110000000</v>
       </c>
-      <c r="D98" s="29" t="n">
+      <c r="D98" s="30" t="n">
         <v>110</v>
       </c>
       <c r="E98" s="29" t="s">
@@ -8320,28 +8325,28 @@
       <c r="G98" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H98" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I98" s="30" t="s">
+      <c r="H98" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I98" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="J98" s="30" t="s">
+      <c r="J98" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="K98" s="30" t="s">
+      <c r="K98" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L98" s="30" t="s">
+      <c r="L98" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M98" s="30" t="s">
+      <c r="M98" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N98" s="30" t="s">
+      <c r="N98" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O98" s="30" t="s">
+      <c r="O98" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8352,10 +8357,10 @@
       <c r="B99" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C99" s="29" t="n">
+      <c r="C99" s="30" t="n">
         <v>863000000</v>
       </c>
-      <c r="D99" s="29" t="n">
+      <c r="D99" s="30" t="n">
         <v>863</v>
       </c>
       <c r="E99" s="29" t="s">
@@ -8367,28 +8372,28 @@
       <c r="G99" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H99" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I99" s="30" t="s">
+      <c r="H99" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I99" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J99" s="30" t="s">
+      <c r="J99" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="K99" s="30" t="s">
+      <c r="K99" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L99" s="30" t="s">
+      <c r="L99" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M99" s="30" t="s">
+      <c r="M99" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N99" s="30" t="s">
+      <c r="N99" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O99" s="30" t="s">
+      <c r="O99" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8399,10 +8404,10 @@
       <c r="B100" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C100" s="29" t="n">
+      <c r="C100" s="30" t="n">
         <v>132000000</v>
       </c>
-      <c r="D100" s="29" t="n">
+      <c r="D100" s="30" t="n">
         <v>132</v>
       </c>
       <c r="E100" s="29" t="s">
@@ -8414,28 +8419,28 @@
       <c r="G100" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H100" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I100" s="30" t="s">
+      <c r="H100" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I100" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="J100" s="30" t="s">
+      <c r="J100" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="K100" s="30" t="s">
+      <c r="K100" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L100" s="30" t="s">
+      <c r="L100" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M100" s="30" t="s">
+      <c r="M100" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N100" s="30" t="s">
+      <c r="N100" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O100" s="30" t="s">
+      <c r="O100" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8446,10 +8451,10 @@
       <c r="B101" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C101" s="29" t="n">
+      <c r="C101" s="30" t="n">
         <v>731000000</v>
       </c>
-      <c r="D101" s="29" t="n">
+      <c r="D101" s="30" t="n">
         <v>731</v>
       </c>
       <c r="E101" s="29" t="s">
@@ -8461,28 +8466,28 @@
       <c r="G101" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H101" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I101" s="30" t="s">
+      <c r="H101" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I101" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="J101" s="30" t="s">
+      <c r="J101" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="K101" s="30" t="s">
+      <c r="K101" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L101" s="30" t="s">
+      <c r="L101" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M101" s="30" t="s">
+      <c r="M101" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N101" s="30" t="s">
+      <c r="N101" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O101" s="30" t="s">
+      <c r="O101" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8493,10 +8498,10 @@
       <c r="B102" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="C102" s="29" t="n">
+      <c r="C102" s="30" t="n">
         <v>-74000000</v>
       </c>
-      <c r="D102" s="29" t="n">
+      <c r="D102" s="30" t="n">
         <v>-74</v>
       </c>
       <c r="E102" s="29" t="s">
@@ -8508,28 +8513,28 @@
       <c r="G102" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H102" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I102" s="30" t="s">
+      <c r="H102" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I102" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="J102" s="30" t="s">
+      <c r="J102" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="K102" s="30" t="s">
+      <c r="K102" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L102" s="30" t="s">
+      <c r="L102" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M102" s="30" t="s">
+      <c r="M102" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N102" s="30" t="s">
+      <c r="N102" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O102" s="30" t="s">
+      <c r="O102" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8547,18 +8552,18 @@
       <c r="G103" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H103" s="30" t="s">
+      <c r="H103" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I103" s="30" t="s">
+      <c r="I103" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="J103" s="30"/>
-      <c r="K103" s="30"/>
-      <c r="L103" s="30"/>
-      <c r="M103" s="30"/>
-      <c r="N103" s="30"/>
-      <c r="O103" s="30"/>
+      <c r="J103" s="31"/>
+      <c r="K103" s="31"/>
+      <c r="L103" s="31"/>
+      <c r="M103" s="31"/>
+      <c r="N103" s="31"/>
+      <c r="O103" s="31"/>
     </row>
     <row r="104" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="29" t="n">
@@ -8567,10 +8572,10 @@
       <c r="B104" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C104" s="29" t="n">
+      <c r="C104" s="30" t="n">
         <v>657000000</v>
       </c>
-      <c r="D104" s="29" t="n">
+      <c r="D104" s="30" t="n">
         <v>657</v>
       </c>
       <c r="E104" s="29" t="s">
@@ -8582,28 +8587,28 @@
       <c r="G104" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H104" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I104" s="30" t="s">
+      <c r="H104" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I104" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="J104" s="30" t="s">
+      <c r="J104" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="K104" s="30" t="s">
+      <c r="K104" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L104" s="30" t="s">
+      <c r="L104" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M104" s="30" t="s">
+      <c r="M104" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N104" s="30" t="s">
+      <c r="N104" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O104" s="30" t="s">
+      <c r="O104" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8614,10 +8619,10 @@
       <c r="B105" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C105" s="29" t="n">
+      <c r="C105" s="30" t="n">
         <v>1.44</v>
       </c>
-      <c r="D105" s="29" t="n">
+      <c r="D105" s="30" t="n">
         <v>1.44</v>
       </c>
       <c r="E105" s="29" t="s">
@@ -8629,28 +8634,28 @@
       <c r="G105" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H105" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I105" s="30" t="s">
+      <c r="H105" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I105" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="J105" s="30" t="s">
+      <c r="J105" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="K105" s="30" t="s">
+      <c r="K105" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L105" s="30" t="s">
+      <c r="L105" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M105" s="30" t="s">
+      <c r="M105" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N105" s="30" t="s">
+      <c r="N105" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O105" s="30" t="s">
+      <c r="O105" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8661,10 +8666,10 @@
       <c r="B106" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="C106" s="29" t="n">
+      <c r="C106" s="30" t="n">
         <v>62698000000</v>
       </c>
-      <c r="D106" s="29" t="n">
+      <c r="D106" s="30" t="n">
         <v>62698</v>
       </c>
       <c r="E106" s="29" t="s">
@@ -8676,28 +8681,28 @@
       <c r="G106" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H106" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I106" s="30" t="s">
+      <c r="H106" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I106" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="J106" s="30" t="s">
+      <c r="J106" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K106" s="30" t="s">
+      <c r="K106" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L106" s="30" t="s">
+      <c r="L106" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M106" s="30" t="s">
+      <c r="M106" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N106" s="30" t="s">
+      <c r="N106" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O106" s="30" t="s">
+      <c r="O106" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8708,10 +8713,10 @@
       <c r="B107" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C107" s="29" t="n">
+      <c r="C107" s="30" t="n">
         <v>5389000000</v>
       </c>
-      <c r="D107" s="29" t="n">
+      <c r="D107" s="30" t="n">
         <v>5389</v>
       </c>
       <c r="E107" s="29" t="s">
@@ -8723,28 +8728,28 @@
       <c r="G107" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H107" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I107" s="30" t="s">
+      <c r="H107" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I107" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="J107" s="30" t="s">
+      <c r="J107" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="K107" s="30" t="s">
+      <c r="K107" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L107" s="30" t="s">
+      <c r="L107" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M107" s="30" t="s">
+      <c r="M107" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N107" s="30" t="s">
+      <c r="N107" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O107" s="30" t="s">
+      <c r="O107" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8755,10 +8760,10 @@
       <c r="B108" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="C108" s="29" t="n">
+      <c r="C108" s="30" t="n">
         <v>79058000000</v>
       </c>
-      <c r="D108" s="29" t="n">
+      <c r="D108" s="30" t="n">
         <v>79058</v>
       </c>
       <c r="E108" s="29" t="s">
@@ -8770,28 +8775,28 @@
       <c r="G108" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H108" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I108" s="30" t="s">
+      <c r="H108" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I108" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="J108" s="30" t="s">
+      <c r="J108" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="K108" s="30" t="s">
+      <c r="K108" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L108" s="30" t="s">
+      <c r="L108" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M108" s="30" t="s">
+      <c r="M108" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N108" s="30" t="s">
+      <c r="N108" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O108" s="30" t="s">
+      <c r="O108" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8802,10 +8807,10 @@
       <c r="B109" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="29" t="n">
+      <c r="C109" s="30" t="n">
         <v>54658000000</v>
       </c>
-      <c r="D109" s="29" t="n">
+      <c r="D109" s="30" t="n">
         <v>54658</v>
       </c>
       <c r="E109" s="29" t="s">
@@ -8817,28 +8822,28 @@
       <c r="G109" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H109" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I109" s="30" t="s">
+      <c r="H109" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I109" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="J109" s="30" t="s">
+      <c r="J109" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="K109" s="30" t="s">
+      <c r="K109" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L109" s="30" t="s">
+      <c r="L109" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M109" s="30" t="s">
+      <c r="M109" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N109" s="30" t="s">
+      <c r="N109" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O109" s="30" t="s">
+      <c r="O109" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8849,10 +8854,10 @@
       <c r="B110" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="C110" s="29" t="n">
+      <c r="C110" s="30" t="n">
         <v>60047000000</v>
       </c>
-      <c r="D110" s="29" t="n">
+      <c r="D110" s="30" t="n">
         <v>60047</v>
       </c>
       <c r="E110" s="29" t="s">
@@ -8864,28 +8869,28 @@
       <c r="G110" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H110" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I110" s="30" t="s">
+      <c r="H110" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I110" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="J110" s="30" t="s">
+      <c r="J110" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="K110" s="30" t="s">
+      <c r="K110" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L110" s="30" t="s">
+      <c r="L110" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M110" s="30" t="s">
+      <c r="M110" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N110" s="30" t="s">
+      <c r="N110" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O110" s="30" t="s">
+      <c r="O110" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8896,10 +8901,10 @@
       <c r="B111" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C111" s="29" t="n">
+      <c r="C111" s="30" t="n">
         <v>8885000000</v>
       </c>
-      <c r="D111" s="29" t="n">
+      <c r="D111" s="30" t="n">
         <v>8885</v>
       </c>
       <c r="E111" s="29" t="s">
@@ -8911,28 +8916,28 @@
       <c r="G111" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H111" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I111" s="30" t="s">
+      <c r="H111" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I111" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="J111" s="30" t="s">
+      <c r="J111" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="K111" s="30" t="s">
+      <c r="K111" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L111" s="30" t="s">
+      <c r="L111" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M111" s="30" t="s">
+      <c r="M111" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N111" s="30" t="s">
+      <c r="N111" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O111" s="30" t="s">
+      <c r="O111" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8943,10 +8948,10 @@
       <c r="B112" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="C112" s="29" t="n">
+      <c r="C112" s="30" t="n">
         <v>7.2</v>
       </c>
-      <c r="D112" s="29" t="n">
+      <c r="D112" s="30" t="n">
         <v>7.2</v>
       </c>
       <c r="E112" s="29" t="s">
@@ -8958,28 +8963,28 @@
       <c r="G112" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H112" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I112" s="30" t="s">
+      <c r="H112" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I112" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="J112" s="30" t="s">
+      <c r="J112" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K112" s="30" t="s">
+      <c r="K112" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L112" s="30" t="s">
+      <c r="L112" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M112" s="30" t="s">
+      <c r="M112" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N112" s="30" t="s">
+      <c r="N112" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O112" s="30" t="s">
+      <c r="O112" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8990,10 +8995,10 @@
       <c r="B113" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="C113" s="29" t="n">
+      <c r="C113" s="30" t="n">
         <v>7.2</v>
       </c>
-      <c r="D113" s="29" t="n">
+      <c r="D113" s="30" t="n">
         <v>7.2</v>
       </c>
       <c r="E113" s="29" t="s">
@@ -9005,28 +9010,28 @@
       <c r="G113" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H113" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I113" s="30" t="s">
+      <c r="H113" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I113" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="J113" s="30" t="s">
+      <c r="J113" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="K113" s="30" t="s">
+      <c r="K113" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L113" s="30" t="s">
+      <c r="L113" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M113" s="30" t="s">
+      <c r="M113" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N113" s="30" t="s">
+      <c r="N113" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O113" s="30" t="s">
+      <c r="O113" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9037,10 +9042,10 @@
       <c r="B114" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C114" s="29" t="n">
+      <c r="C114" s="30" t="n">
         <v>0.132</v>
       </c>
-      <c r="D114" s="29" t="n">
+      <c r="D114" s="30" t="n">
         <v>13.2</v>
       </c>
       <c r="E114" s="29" t="s">
@@ -9052,28 +9057,28 @@
       <c r="G114" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H114" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I114" s="30" t="s">
+      <c r="H114" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I114" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="J114" s="30" t="s">
+      <c r="J114" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K114" s="30" t="s">
+      <c r="K114" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L114" s="30" t="s">
+      <c r="L114" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M114" s="30" t="s">
+      <c r="M114" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N114" s="30" t="s">
+      <c r="N114" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O114" s="30" t="s">
+      <c r="O114" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9087,7 +9092,7 @@
       <c r="C115" s="29" t="n">
         <v>0.0014</v>
       </c>
-      <c r="D115" s="29" t="n">
+      <c r="D115" s="30" t="n">
         <v>0.14</v>
       </c>
       <c r="E115" s="29" t="s">
@@ -9099,28 +9104,28 @@
       <c r="G115" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H115" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I115" s="30" t="s">
+      <c r="H115" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I115" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="J115" s="30" t="s">
+      <c r="J115" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K115" s="30" t="s">
+      <c r="K115" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L115" s="30" t="s">
+      <c r="L115" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M115" s="30" t="s">
+      <c r="M115" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N115" s="30" t="s">
+      <c r="N115" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O115" s="30" t="s">
+      <c r="O115" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9131,10 +9136,10 @@
       <c r="B116" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="C116" s="29" t="n">
+      <c r="C116" s="30" t="n">
         <v>0.047</v>
       </c>
-      <c r="D116" s="29" t="n">
+      <c r="D116" s="30" t="n">
         <v>4.7</v>
       </c>
       <c r="E116" s="29" t="s">
@@ -9146,28 +9151,28 @@
       <c r="G116" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H116" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I116" s="30" t="s">
+      <c r="H116" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I116" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="J116" s="30" t="s">
+      <c r="J116" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="K116" s="30" t="s">
+      <c r="K116" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L116" s="30" t="s">
+      <c r="L116" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M116" s="30" t="s">
+      <c r="M116" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N116" s="30" t="s">
+      <c r="N116" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O116" s="30" t="s">
+      <c r="O116" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9178,10 +9183,10 @@
       <c r="B117" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="C117" s="29" t="n">
+      <c r="C117" s="30" t="n">
         <v>0.0228</v>
       </c>
-      <c r="D117" s="29" t="n">
+      <c r="D117" s="30" t="n">
         <v>2.28</v>
       </c>
       <c r="E117" s="29" t="s">
@@ -9193,28 +9198,28 @@
       <c r="G117" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H117" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I117" s="30" t="s">
+      <c r="H117" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I117" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="J117" s="30" t="s">
+      <c r="J117" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="K117" s="30" t="s">
+      <c r="K117" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L117" s="30" t="s">
+      <c r="L117" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M117" s="30" t="s">
+      <c r="M117" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N117" s="30" t="s">
+      <c r="N117" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O117" s="30" t="s">
+      <c r="O117" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9225,10 +9230,10 @@
       <c r="B118" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="C118" s="29" t="n">
+      <c r="C118" s="30" t="n">
         <v>0.0242</v>
       </c>
-      <c r="D118" s="29" t="n">
+      <c r="D118" s="30" t="n">
         <v>2.42</v>
       </c>
       <c r="E118" s="29" t="s">
@@ -9240,28 +9245,28 @@
       <c r="G118" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H118" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I118" s="30" t="s">
+      <c r="H118" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I118" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="J118" s="30" t="s">
+      <c r="J118" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="K118" s="30" t="s">
+      <c r="K118" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L118" s="30" t="s">
+      <c r="L118" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M118" s="30" t="s">
+      <c r="M118" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N118" s="30" t="s">
+      <c r="N118" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O118" s="30" t="s">
+      <c r="O118" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9272,10 +9277,10 @@
       <c r="B119" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="C119" s="29" t="n">
+      <c r="C119" s="30" t="n">
         <v>43351000000</v>
       </c>
-      <c r="D119" s="29" t="n">
+      <c r="D119" s="30" t="n">
         <v>43351</v>
       </c>
       <c r="E119" s="29" t="s">
@@ -9287,28 +9292,28 @@
       <c r="G119" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H119" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I119" s="30" t="s">
+      <c r="H119" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I119" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="J119" s="30" t="s">
+      <c r="J119" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="K119" s="30" t="s">
+      <c r="K119" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L119" s="30" t="s">
+      <c r="L119" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M119" s="30" t="s">
+      <c r="M119" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N119" s="30" t="s">
+      <c r="N119" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O119" s="30" t="s">
+      <c r="O119" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9319,10 +9324,10 @@
       <c r="B120" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="C120" s="29" t="n">
+      <c r="C120" s="30" t="n">
         <v>0.72</v>
       </c>
-      <c r="D120" s="29" t="n">
+      <c r="D120" s="30" t="n">
         <v>72</v>
       </c>
       <c r="E120" s="29" t="s">
@@ -9334,28 +9339,28 @@
       <c r="G120" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H120" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I120" s="30" t="s">
+      <c r="H120" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I120" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="J120" s="30" t="s">
+      <c r="J120" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="K120" s="30" t="s">
+      <c r="K120" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L120" s="30" t="s">
+      <c r="L120" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M120" s="30" t="s">
+      <c r="M120" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N120" s="30" t="s">
+      <c r="N120" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O120" s="30" t="s">
+      <c r="O120" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9366,10 +9371,10 @@
       <c r="B121" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="29" t="n">
+      <c r="C121" s="30" t="n">
         <v>-0.0409</v>
       </c>
-      <c r="D121" s="29" t="n">
+      <c r="D121" s="30" t="n">
         <v>-4.09</v>
       </c>
       <c r="E121" s="29" t="s">
@@ -9381,28 +9386,28 @@
       <c r="G121" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H121" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I121" s="30" t="s">
+      <c r="H121" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I121" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="J121" s="30" t="s">
+      <c r="J121" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="K121" s="30" t="s">
+      <c r="K121" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L121" s="30" t="s">
+      <c r="L121" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="M121" s="30" t="s">
+      <c r="M121" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N121" s="30" t="s">
+      <c r="N121" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O121" s="30" t="s">
+      <c r="O121" s="31" t="s">
         <v>292</v>
       </c>
     </row>
@@ -9413,10 +9418,10 @@
       <c r="B122" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C122" s="29" t="n">
+      <c r="C122" s="30" t="n">
         <v>81789000000</v>
       </c>
-      <c r="D122" s="29" t="n">
+      <c r="D122" s="30" t="n">
         <v>81789</v>
       </c>
       <c r="E122" s="29" t="s">
@@ -9428,28 +9433,28 @@
       <c r="G122" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H122" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I122" s="30" t="s">
+      <c r="H122" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I122" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="J122" s="30" t="s">
+      <c r="J122" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="K122" s="30" t="s">
+      <c r="K122" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L122" s="30" t="s">
+      <c r="L122" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M122" s="30" t="s">
+      <c r="M122" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N122" s="30" t="s">
+      <c r="N122" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O122" s="30" t="s">
+      <c r="O122" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9460,10 +9465,10 @@
       <c r="B123" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C123" s="29" t="n">
+      <c r="C123" s="30" t="n">
         <v>115077000000</v>
       </c>
-      <c r="D123" s="29" t="n">
+      <c r="D123" s="30" t="n">
         <v>115077</v>
       </c>
       <c r="E123" s="29" t="s">
@@ -9475,28 +9480,28 @@
       <c r="G123" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H123" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I123" s="30" t="s">
+      <c r="H123" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I123" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="J123" s="30" t="s">
+      <c r="J123" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="K123" s="30" t="s">
+      <c r="K123" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L123" s="30" t="s">
+      <c r="L123" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M123" s="30" t="s">
+      <c r="M123" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N123" s="30" t="s">
+      <c r="N123" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O123" s="30" t="s">
+      <c r="O123" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9507,10 +9512,10 @@
       <c r="B124" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="C124" s="29" t="n">
+      <c r="C124" s="30" t="n">
         <v>85342000000</v>
       </c>
-      <c r="D124" s="29" t="n">
+      <c r="D124" s="30" t="n">
         <v>85342</v>
       </c>
       <c r="E124" s="29" t="s">
@@ -9522,28 +9527,28 @@
       <c r="G124" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H124" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I124" s="30" t="s">
+      <c r="H124" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I124" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J124" s="30" t="s">
+      <c r="J124" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="K124" s="30" t="s">
+      <c r="K124" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L124" s="30" t="s">
+      <c r="L124" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M124" s="30" t="s">
+      <c r="M124" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N124" s="30" t="s">
+      <c r="N124" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O124" s="30" t="s">
+      <c r="O124" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9554,10 +9559,10 @@
       <c r="B125" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C125" s="29" t="n">
+      <c r="C125" s="30" t="n">
         <v>102684000000</v>
       </c>
-      <c r="D125" s="29" t="n">
+      <c r="D125" s="30" t="n">
         <v>102684</v>
       </c>
       <c r="E125" s="29" t="s">
@@ -9569,28 +9574,28 @@
       <c r="G125" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H125" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I125" s="30" t="s">
+      <c r="H125" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I125" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="J125" s="30" t="s">
+      <c r="J125" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="K125" s="30" t="s">
+      <c r="K125" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L125" s="30" t="s">
+      <c r="L125" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M125" s="30" t="s">
+      <c r="M125" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N125" s="30" t="s">
+      <c r="N125" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O125" s="30" t="s">
+      <c r="O125" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9601,10 +9606,10 @@
       <c r="B126" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C126" s="29" t="n">
+      <c r="C126" s="30" t="n">
         <v>12393000000</v>
       </c>
-      <c r="D126" s="29" t="n">
+      <c r="D126" s="30" t="n">
         <v>12393</v>
       </c>
       <c r="E126" s="29" t="s">
@@ -9616,28 +9621,28 @@
       <c r="G126" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H126" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I126" s="30" t="s">
+      <c r="H126" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I126" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J126" s="30" t="s">
+      <c r="J126" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="K126" s="30" t="s">
+      <c r="K126" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L126" s="30" t="s">
+      <c r="L126" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M126" s="30" t="s">
+      <c r="M126" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N126" s="30" t="s">
+      <c r="N126" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O126" s="30" t="s">
+      <c r="O126" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9648,10 +9653,10 @@
       <c r="B127" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="C127" s="29" t="n">
+      <c r="C127" s="30" t="n">
         <v>9.35</v>
       </c>
-      <c r="D127" s="29" t="n">
+      <c r="D127" s="30" t="n">
         <v>9.35</v>
       </c>
       <c r="E127" s="29" t="s">
@@ -9663,28 +9668,28 @@
       <c r="G127" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H127" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I127" s="30" t="s">
+      <c r="H127" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I127" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="J127" s="30" t="s">
+      <c r="J127" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="K127" s="30" t="s">
+      <c r="K127" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L127" s="30" t="s">
+      <c r="L127" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M127" s="30" t="s">
+      <c r="M127" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N127" s="30" t="s">
+      <c r="N127" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O127" s="30" t="s">
+      <c r="O127" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9695,10 +9700,10 @@
       <c r="B128" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C128" s="29" t="n">
+      <c r="C128" s="30" t="n">
         <v>8.88</v>
       </c>
-      <c r="D128" s="29" t="n">
+      <c r="D128" s="30" t="n">
         <v>8.88</v>
       </c>
       <c r="E128" s="29" t="s">
@@ -9710,28 +9715,28 @@
       <c r="G128" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H128" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I128" s="30" t="s">
+      <c r="H128" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I128" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="J128" s="30" t="s">
+      <c r="J128" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="K128" s="30" t="s">
+      <c r="K128" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="L128" s="30" t="s">
+      <c r="L128" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M128" s="30" t="s">
+      <c r="M128" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N128" s="30" t="s">
+      <c r="N128" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O128" s="30" t="s">
+      <c r="O128" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9742,10 +9747,10 @@
       <c r="B129" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C129" s="29" t="n">
+      <c r="C129" s="30" t="n">
         <v>1107600000</v>
       </c>
-      <c r="D129" s="29" t="n">
+      <c r="D129" s="30" t="n">
         <v>1107.6</v>
       </c>
       <c r="E129" s="29" t="s">
@@ -9757,28 +9762,28 @@
       <c r="G129" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H129" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I129" s="30" t="s">
+      <c r="H129" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I129" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="J129" s="30" t="s">
+      <c r="J129" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="K129" s="30" t="s">
+      <c r="K129" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="L129" s="30" t="s">
+      <c r="L129" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M129" s="30" t="s">
+      <c r="M129" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N129" s="30" t="s">
+      <c r="N129" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O129" s="30" t="s">
+      <c r="O129" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9789,10 +9794,10 @@
       <c r="B130" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="C130" s="29" t="n">
+      <c r="C130" s="30" t="n">
         <v>1968000000</v>
       </c>
-      <c r="D130" s="29" t="n">
+      <c r="D130" s="30" t="n">
         <v>1968</v>
       </c>
       <c r="E130" s="29" t="s">
@@ -9804,28 +9809,28 @@
       <c r="G130" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H130" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I130" s="30" t="s">
+      <c r="H130" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I130" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="J130" s="30" t="s">
+      <c r="J130" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="K130" s="30" t="s">
+      <c r="K130" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="L130" s="30" t="s">
+      <c r="L130" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M130" s="30" t="s">
+      <c r="M130" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N130" s="30" t="s">
+      <c r="N130" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O130" s="30" t="s">
+      <c r="O130" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9836,10 +9841,10 @@
       <c r="B131" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="C131" s="29" t="n">
+      <c r="C131" s="30" t="n">
         <v>2033000000</v>
       </c>
-      <c r="D131" s="29" t="n">
+      <c r="D131" s="30" t="n">
         <v>2033</v>
       </c>
       <c r="E131" s="29" t="s">
@@ -9851,28 +9856,28 @@
       <c r="G131" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H131" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I131" s="30" t="s">
+      <c r="H131" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I131" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="J131" s="30" t="s">
+      <c r="J131" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="K131" s="30" t="s">
+      <c r="K131" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="L131" s="30" t="s">
+      <c r="L131" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M131" s="30" t="s">
+      <c r="M131" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N131" s="30" t="s">
+      <c r="N131" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O131" s="30" t="s">
+      <c r="O131" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9883,10 +9888,10 @@
       <c r="B132" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C132" s="29" t="n">
+      <c r="C132" s="30" t="n">
         <v>3523000000</v>
       </c>
-      <c r="D132" s="29" t="n">
+      <c r="D132" s="30" t="n">
         <v>3523</v>
       </c>
       <c r="E132" s="29" t="s">
@@ -9898,28 +9903,28 @@
       <c r="G132" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H132" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I132" s="30" t="s">
+      <c r="H132" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I132" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="J132" s="30" t="s">
+      <c r="J132" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="K132" s="30" t="s">
+      <c r="K132" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L132" s="30" t="s">
+      <c r="L132" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M132" s="30" t="s">
+      <c r="M132" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N132" s="30" t="s">
+      <c r="N132" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O132" s="30" t="s">
+      <c r="O132" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9930,10 +9935,10 @@
       <c r="B133" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C133" s="29" t="n">
+      <c r="C133" s="30" t="n">
         <v>2848000000</v>
       </c>
-      <c r="D133" s="29" t="n">
+      <c r="D133" s="30" t="n">
         <v>2848</v>
       </c>
       <c r="E133" s="29" t="s">
@@ -9945,28 +9950,28 @@
       <c r="G133" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H133" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I133" s="30" t="s">
+      <c r="H133" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I133" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="J133" s="30" t="s">
+      <c r="J133" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K133" s="30" t="s">
+      <c r="K133" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L133" s="30" t="s">
+      <c r="L133" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M133" s="30" t="s">
+      <c r="M133" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N133" s="30" t="s">
+      <c r="N133" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O133" s="30" t="s">
+      <c r="O133" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -9977,10 +9982,10 @@
       <c r="B134" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C134" s="29" t="n">
+      <c r="C134" s="30" t="n">
         <v>675000000</v>
       </c>
-      <c r="D134" s="29" t="n">
+      <c r="D134" s="30" t="n">
         <v>675</v>
       </c>
       <c r="E134" s="29" t="s">
@@ -9992,28 +9997,28 @@
       <c r="G134" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H134" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I134" s="30" t="s">
+      <c r="H134" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I134" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="J134" s="30" t="s">
+      <c r="J134" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K134" s="30" t="s">
+      <c r="K134" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L134" s="30" t="s">
+      <c r="L134" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M134" s="30" t="s">
+      <c r="M134" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N134" s="30" t="s">
+      <c r="N134" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O134" s="30" t="s">
+      <c r="O134" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10024,10 +10029,10 @@
       <c r="B135" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="C135" s="29" t="n">
+      <c r="C135" s="30" t="n">
         <v>4097000000</v>
       </c>
-      <c r="D135" s="29" t="n">
+      <c r="D135" s="30" t="n">
         <v>4097</v>
       </c>
       <c r="E135" s="29" t="s">
@@ -10039,28 +10044,28 @@
       <c r="G135" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H135" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I135" s="30" t="s">
+      <c r="H135" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I135" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="J135" s="30" t="s">
+      <c r="J135" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="K135" s="30" t="s">
+      <c r="K135" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="L135" s="30" t="s">
+      <c r="L135" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M135" s="30" t="s">
+      <c r="M135" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N135" s="30" t="s">
+      <c r="N135" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O135" s="30" t="s">
+      <c r="O135" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10071,10 +10076,10 @@
       <c r="B136" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C136" s="29" t="n">
+      <c r="C136" s="30" t="n">
         <v>2276000000</v>
       </c>
-      <c r="D136" s="29" t="n">
+      <c r="D136" s="30" t="n">
         <v>2276</v>
       </c>
       <c r="E136" s="29" t="s">
@@ -10086,28 +10091,28 @@
       <c r="G136" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H136" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I136" s="30" t="s">
+      <c r="H136" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I136" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="J136" s="30" t="s">
+      <c r="J136" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="K136" s="30" t="s">
+      <c r="K136" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="L136" s="30" t="s">
+      <c r="L136" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M136" s="30" t="s">
+      <c r="M136" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N136" s="30" t="s">
+      <c r="N136" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O136" s="30" t="s">
+      <c r="O136" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10118,10 +10123,10 @@
       <c r="B137" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C137" s="29" t="n">
+      <c r="C137" s="30" t="n">
         <v>1122000000</v>
       </c>
-      <c r="D137" s="29" t="n">
+      <c r="D137" s="30" t="n">
         <v>1122</v>
       </c>
       <c r="E137" s="29" t="s">
@@ -10133,28 +10138,28 @@
       <c r="G137" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H137" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I137" s="30" t="s">
+      <c r="H137" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I137" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="J137" s="30" t="s">
+      <c r="J137" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="K137" s="30" t="s">
+      <c r="K137" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L137" s="30" t="s">
+      <c r="L137" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M137" s="30" t="s">
+      <c r="M137" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N137" s="30" t="s">
+      <c r="N137" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O137" s="30" t="s">
+      <c r="O137" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10165,10 +10170,10 @@
       <c r="B138" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C138" s="29" t="n">
+      <c r="C138" s="30" t="n">
         <v>127000000</v>
       </c>
-      <c r="D138" s="29" t="n">
+      <c r="D138" s="30" t="n">
         <v>127</v>
       </c>
       <c r="E138" s="29" t="s">
@@ -10180,28 +10185,28 @@
       <c r="G138" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H138" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I138" s="30" t="s">
+      <c r="H138" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I138" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="J138" s="30" t="s">
+      <c r="J138" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="K138" s="30" t="s">
+      <c r="K138" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L138" s="30" t="s">
+      <c r="L138" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M138" s="30" t="s">
+      <c r="M138" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N138" s="30" t="s">
+      <c r="N138" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O138" s="30" t="s">
+      <c r="O138" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10212,10 +10217,10 @@
       <c r="B139" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C139" s="29" t="n">
+      <c r="C139" s="30" t="n">
         <v>1670000000</v>
       </c>
-      <c r="D139" s="29" t="n">
+      <c r="D139" s="30" t="n">
         <v>1670</v>
       </c>
       <c r="E139" s="29" t="s">
@@ -10227,28 +10232,28 @@
       <c r="G139" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H139" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I139" s="30" t="s">
+      <c r="H139" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I139" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J139" s="30" t="s">
+      <c r="J139" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="K139" s="30" t="s">
+      <c r="K139" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L139" s="30" t="s">
+      <c r="L139" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M139" s="30" t="s">
+      <c r="M139" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N139" s="30" t="s">
+      <c r="N139" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O139" s="30" t="s">
+      <c r="O139" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10259,10 +10264,10 @@
       <c r="B140" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C140" s="29" t="n">
+      <c r="C140" s="30" t="n">
         <v>161000000</v>
       </c>
-      <c r="D140" s="29" t="n">
+      <c r="D140" s="30" t="n">
         <v>161</v>
       </c>
       <c r="E140" s="29" t="s">
@@ -10274,28 +10279,28 @@
       <c r="G140" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H140" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I140" s="30" t="s">
+      <c r="H140" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I140" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="J140" s="30" t="s">
+      <c r="J140" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="K140" s="30" t="s">
+      <c r="K140" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L140" s="30" t="s">
+      <c r="L140" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M140" s="30" t="s">
+      <c r="M140" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N140" s="30" t="s">
+      <c r="N140" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O140" s="30" t="s">
+      <c r="O140" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10306,10 +10311,10 @@
       <c r="B141" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C141" s="29" t="n">
+      <c r="C141" s="30" t="n">
         <v>1509000000</v>
       </c>
-      <c r="D141" s="29" t="n">
+      <c r="D141" s="30" t="n">
         <v>1509</v>
       </c>
       <c r="E141" s="29" t="s">
@@ -10321,28 +10326,28 @@
       <c r="G141" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H141" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I141" s="30" t="s">
+      <c r="H141" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I141" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="J141" s="30" t="s">
+      <c r="J141" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="K141" s="30" t="s">
+      <c r="K141" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L141" s="30" t="s">
+      <c r="L141" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M141" s="30" t="s">
+      <c r="M141" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N141" s="30" t="s">
+      <c r="N141" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O141" s="30" t="s">
+      <c r="O141" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10353,10 +10358,10 @@
       <c r="B142" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="C142" s="29" t="n">
+      <c r="C142" s="30" t="n">
         <v>268000000</v>
       </c>
-      <c r="D142" s="29" t="n">
+      <c r="D142" s="30" t="n">
         <v>268</v>
       </c>
       <c r="E142" s="29" t="s">
@@ -10368,28 +10373,28 @@
       <c r="G142" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H142" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I142" s="30" t="s">
+      <c r="H142" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I142" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="J142" s="30" t="s">
+      <c r="J142" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="K142" s="30" t="s">
+      <c r="K142" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L142" s="30" t="s">
+      <c r="L142" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M142" s="30" t="s">
+      <c r="M142" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N142" s="30" t="s">
+      <c r="N142" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O142" s="30" t="s">
+      <c r="O142" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10407,18 +10412,18 @@
       <c r="G143" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H143" s="30" t="s">
+      <c r="H143" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I143" s="30" t="s">
+      <c r="I143" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="J143" s="30"/>
-      <c r="K143" s="30"/>
-      <c r="L143" s="30"/>
-      <c r="M143" s="30"/>
-      <c r="N143" s="30"/>
-      <c r="O143" s="30"/>
+      <c r="J143" s="31"/>
+      <c r="K143" s="31"/>
+      <c r="L143" s="31"/>
+      <c r="M143" s="31"/>
+      <c r="N143" s="31"/>
+      <c r="O143" s="31"/>
     </row>
     <row r="144" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="29" t="n">
@@ -10427,10 +10432,10 @@
       <c r="B144" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C144" s="29" t="n">
+      <c r="C144" s="30" t="n">
         <v>1777000000</v>
       </c>
-      <c r="D144" s="29" t="n">
+      <c r="D144" s="30" t="n">
         <v>1777</v>
       </c>
       <c r="E144" s="29" t="s">
@@ -10442,28 +10447,28 @@
       <c r="G144" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H144" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I144" s="30" t="s">
+      <c r="H144" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I144" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="J144" s="30" t="s">
+      <c r="J144" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="K144" s="30" t="s">
+      <c r="K144" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L144" s="30" t="s">
+      <c r="L144" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M144" s="30" t="s">
+      <c r="M144" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N144" s="30" t="s">
+      <c r="N144" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O144" s="30" t="s">
+      <c r="O144" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10474,10 +10479,10 @@
       <c r="B145" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C145" s="29" t="n">
+      <c r="C145" s="30" t="n">
         <v>1.44</v>
       </c>
-      <c r="D145" s="29" t="n">
+      <c r="D145" s="30" t="n">
         <v>1.44</v>
       </c>
       <c r="E145" s="29" t="s">
@@ -10489,28 +10494,28 @@
       <c r="G145" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H145" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I145" s="30" t="s">
+      <c r="H145" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I145" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="J145" s="30" t="s">
+      <c r="J145" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="K145" s="30" t="s">
+      <c r="K145" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="L145" s="30" t="s">
+      <c r="L145" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M145" s="30" t="s">
+      <c r="M145" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N145" s="30" t="s">
+      <c r="N145" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O145" s="30" t="s">
+      <c r="O145" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10521,10 +10526,10 @@
       <c r="B146" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="C146" s="29" t="n">
+      <c r="C146" s="30" t="n">
         <v>72737000000</v>
       </c>
-      <c r="D146" s="29" t="n">
+      <c r="D146" s="30" t="n">
         <v>72737</v>
       </c>
       <c r="E146" s="29" t="s">
@@ -10536,28 +10541,28 @@
       <c r="G146" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H146" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I146" s="30" t="s">
+      <c r="H146" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I146" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="J146" s="30" t="s">
+      <c r="J146" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K146" s="30" t="s">
+      <c r="K146" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L146" s="30" t="s">
+      <c r="L146" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M146" s="30" t="s">
+      <c r="M146" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N146" s="30" t="s">
+      <c r="N146" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O146" s="30" t="s">
+      <c r="O146" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10568,10 +10573,10 @@
       <c r="B147" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C147" s="29" t="n">
+      <c r="C147" s="30" t="n">
         <v>10853000000</v>
       </c>
-      <c r="D147" s="29" t="n">
+      <c r="D147" s="30" t="n">
         <v>10853</v>
       </c>
       <c r="E147" s="29" t="s">
@@ -10583,28 +10588,28 @@
       <c r="G147" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H147" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I147" s="30" t="s">
+      <c r="H147" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I147" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="J147" s="30" t="s">
+      <c r="J147" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="K147" s="30" t="s">
+      <c r="K147" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L147" s="30" t="s">
+      <c r="L147" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M147" s="30" t="s">
+      <c r="M147" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N147" s="30" t="s">
+      <c r="N147" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O147" s="30" t="s">
+      <c r="O147" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10615,10 +10620,10 @@
       <c r="B148" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="C148" s="29" t="n">
+      <c r="C148" s="30" t="n">
         <v>100770000000</v>
       </c>
-      <c r="D148" s="29" t="n">
+      <c r="D148" s="30" t="n">
         <v>100770</v>
       </c>
       <c r="E148" s="29" t="s">
@@ -10630,28 +10635,28 @@
       <c r="G148" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H148" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I148" s="30" t="s">
+      <c r="H148" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I148" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="J148" s="30" t="s">
+      <c r="J148" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="K148" s="30" t="s">
+      <c r="K148" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L148" s="30" t="s">
+      <c r="L148" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M148" s="30" t="s">
+      <c r="M148" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N148" s="30" t="s">
+      <c r="N148" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O148" s="30" t="s">
+      <c r="O148" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10662,10 +10667,10 @@
       <c r="B149" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C149" s="29" t="n">
+      <c r="C149" s="30" t="n">
         <v>64472000000</v>
       </c>
-      <c r="D149" s="29" t="n">
+      <c r="D149" s="30" t="n">
         <v>64472</v>
       </c>
       <c r="E149" s="29" t="s">
@@ -10677,28 +10682,28 @@
       <c r="G149" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H149" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I149" s="30" t="s">
+      <c r="H149" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I149" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="J149" s="30" t="s">
+      <c r="J149" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="K149" s="30" t="s">
+      <c r="K149" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L149" s="30" t="s">
+      <c r="L149" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M149" s="30" t="s">
+      <c r="M149" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N149" s="30" t="s">
+      <c r="N149" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O149" s="30" t="s">
+      <c r="O149" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10709,10 +10714,10 @@
       <c r="B150" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="C150" s="29" t="n">
+      <c r="C150" s="30" t="n">
         <v>75325000000</v>
       </c>
-      <c r="D150" s="29" t="n">
+      <c r="D150" s="30" t="n">
         <v>75325</v>
       </c>
       <c r="E150" s="29" t="s">
@@ -10724,28 +10729,28 @@
       <c r="G150" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H150" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I150" s="30" t="s">
+      <c r="H150" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I150" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="J150" s="30" t="s">
+      <c r="J150" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="K150" s="30" t="s">
+      <c r="K150" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L150" s="30" t="s">
+      <c r="L150" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M150" s="30" t="s">
+      <c r="M150" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N150" s="30" t="s">
+      <c r="N150" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O150" s="30" t="s">
+      <c r="O150" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10756,10 +10761,10 @@
       <c r="B151" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C151" s="29" t="n">
+      <c r="C151" s="30" t="n">
         <v>10663000000</v>
       </c>
-      <c r="D151" s="29" t="n">
+      <c r="D151" s="30" t="n">
         <v>10663</v>
       </c>
       <c r="E151" s="29" t="s">
@@ -10771,28 +10776,28 @@
       <c r="G151" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H151" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I151" s="30" t="s">
+      <c r="H151" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I151" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="J151" s="30" t="s">
+      <c r="J151" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="K151" s="30" t="s">
+      <c r="K151" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L151" s="30" t="s">
+      <c r="L151" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M151" s="30" t="s">
+      <c r="M151" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N151" s="30" t="s">
+      <c r="N151" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O151" s="30" t="s">
+      <c r="O151" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10803,10 +10808,10 @@
       <c r="B152" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="C152" s="29" t="n">
+      <c r="C152" s="30" t="n">
         <v>7.4</v>
       </c>
-      <c r="D152" s="29" t="n">
+      <c r="D152" s="30" t="n">
         <v>7.4</v>
       </c>
       <c r="E152" s="29" t="s">
@@ -10818,28 +10823,28 @@
       <c r="G152" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H152" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I152" s="30" t="s">
+      <c r="H152" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I152" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="J152" s="30" t="s">
+      <c r="J152" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K152" s="30" t="s">
+      <c r="K152" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L152" s="30" t="s">
+      <c r="L152" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M152" s="30" t="s">
+      <c r="M152" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N152" s="30" t="s">
+      <c r="N152" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O152" s="30" t="s">
+      <c r="O152" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10850,10 +10855,10 @@
       <c r="B153" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="C153" s="29" t="n">
+      <c r="C153" s="30" t="n">
         <v>7.2</v>
       </c>
-      <c r="D153" s="29" t="n">
+      <c r="D153" s="30" t="n">
         <v>7.2</v>
       </c>
       <c r="E153" s="29" t="s">
@@ -10865,28 +10870,28 @@
       <c r="G153" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H153" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I153" s="30" t="s">
+      <c r="H153" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I153" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="J153" s="30" t="s">
+      <c r="J153" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="K153" s="30" t="s">
+      <c r="K153" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L153" s="30" t="s">
+      <c r="L153" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M153" s="30" t="s">
+      <c r="M153" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N153" s="30" t="s">
+      <c r="N153" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O153" s="30" t="s">
+      <c r="O153" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10897,10 +10902,10 @@
       <c r="B154" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C154" s="29" t="n">
+      <c r="C154" s="30" t="n">
         <v>0.227</v>
       </c>
-      <c r="D154" s="29" t="n">
+      <c r="D154" s="30" t="n">
         <v>22.7</v>
       </c>
       <c r="E154" s="29" t="s">
@@ -10912,28 +10917,28 @@
       <c r="G154" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H154" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I154" s="30" t="s">
+      <c r="H154" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I154" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="J154" s="30" t="s">
+      <c r="J154" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="K154" s="30" t="s">
+      <c r="K154" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L154" s="30" t="s">
+      <c r="L154" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M154" s="30" t="s">
+      <c r="M154" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N154" s="30" t="s">
+      <c r="N154" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O154" s="30" t="s">
+      <c r="O154" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10947,7 +10952,7 @@
       <c r="C155" s="29" t="n">
         <v>0.0013</v>
       </c>
-      <c r="D155" s="29" t="n">
+      <c r="D155" s="30" t="n">
         <v>0.13</v>
       </c>
       <c r="E155" s="29" t="s">
@@ -10959,28 +10964,28 @@
       <c r="G155" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H155" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I155" s="30" t="s">
+      <c r="H155" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I155" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="J155" s="30" t="s">
+      <c r="J155" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K155" s="30" t="s">
+      <c r="K155" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="L155" s="30" t="s">
+      <c r="L155" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M155" s="30" t="s">
+      <c r="M155" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N155" s="30" t="s">
+      <c r="N155" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O155" s="30" t="s">
+      <c r="O155" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10991,10 +10996,10 @@
       <c r="B156" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="C156" s="29" t="n">
+      <c r="C156" s="30" t="n">
         <v>0.049</v>
       </c>
-      <c r="D156" s="29" t="n">
+      <c r="D156" s="30" t="n">
         <v>4.9</v>
       </c>
       <c r="E156" s="29" t="s">
@@ -11006,28 +11011,28 @@
       <c r="G156" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H156" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I156" s="30" t="s">
+      <c r="H156" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I156" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="J156" s="30" t="s">
+      <c r="J156" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="K156" s="30" t="s">
+      <c r="K156" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L156" s="30" t="s">
+      <c r="L156" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M156" s="30" t="s">
+      <c r="M156" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N156" s="30" t="s">
+      <c r="N156" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O156" s="30" t="s">
+      <c r="O156" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11038,10 +11043,10 @@
       <c r="B157" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="C157" s="29" t="n">
+      <c r="C157" s="30" t="n">
         <v>0.0298</v>
       </c>
-      <c r="D157" s="29" t="n">
+      <c r="D157" s="30" t="n">
         <v>2.98</v>
       </c>
       <c r="E157" s="29" t="s">
@@ -11053,28 +11058,28 @@
       <c r="G157" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H157" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I157" s="30" t="s">
+      <c r="H157" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I157" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="J157" s="30" t="s">
+      <c r="J157" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="K157" s="30" t="s">
+      <c r="K157" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L157" s="30" t="s">
+      <c r="L157" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M157" s="30" t="s">
+      <c r="M157" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N157" s="30" t="s">
+      <c r="N157" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O157" s="30" t="s">
+      <c r="O157" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11085,10 +11090,10 @@
       <c r="B158" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="C158" s="29" t="n">
+      <c r="C158" s="30" t="n">
         <v>0.0192</v>
       </c>
-      <c r="D158" s="29" t="n">
+      <c r="D158" s="30" t="n">
         <v>1.92</v>
       </c>
       <c r="E158" s="29" t="s">
@@ -11100,28 +11105,28 @@
       <c r="G158" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H158" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I158" s="30" t="s">
+      <c r="H158" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I158" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="J158" s="30" t="s">
+      <c r="J158" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="K158" s="30" t="s">
+      <c r="K158" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="L158" s="30" t="s">
+      <c r="L158" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M158" s="30" t="s">
+      <c r="M158" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N158" s="30" t="s">
+      <c r="N158" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O158" s="30" t="s">
+      <c r="O158" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11132,10 +11137,10 @@
       <c r="B159" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="C159" s="29" t="n">
+      <c r="C159" s="30" t="n">
         <v>48921000000</v>
       </c>
-      <c r="D159" s="29" t="n">
+      <c r="D159" s="30" t="n">
         <v>48921</v>
       </c>
       <c r="E159" s="29" t="s">
@@ -11147,28 +11152,28 @@
       <c r="G159" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H159" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I159" s="30" t="s">
+      <c r="H159" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I159" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="J159" s="30" t="s">
+      <c r="J159" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="K159" s="30" t="s">
+      <c r="K159" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L159" s="30" t="s">
+      <c r="L159" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M159" s="30" t="s">
+      <c r="M159" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N159" s="30" t="s">
+      <c r="N159" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O159" s="30" t="s">
+      <c r="O159" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11179,10 +11184,10 @@
       <c r="B160" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="C160" s="29" t="n">
+      <c r="C160" s="30" t="n">
         <v>0.65</v>
       </c>
-      <c r="D160" s="29" t="n">
+      <c r="D160" s="30" t="n">
         <v>65</v>
       </c>
       <c r="E160" s="29" t="s">
@@ -11194,28 +11199,28 @@
       <c r="G160" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H160" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I160" s="30" t="s">
+      <c r="H160" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I160" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="J160" s="30" t="s">
+      <c r="J160" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="K160" s="30" t="s">
+      <c r="K160" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L160" s="30" t="s">
+      <c r="L160" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M160" s="30" t="s">
+      <c r="M160" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N160" s="30" t="s">
+      <c r="N160" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O160" s="30" t="s">
+      <c r="O160" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11226,10 +11231,10 @@
       <c r="B161" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="C161" s="29" t="n">
+      <c r="C161" s="30" t="n">
         <v>-0.0218</v>
       </c>
-      <c r="D161" s="29" t="n">
+      <c r="D161" s="30" t="n">
         <v>-2.18</v>
       </c>
       <c r="E161" s="29" t="s">
@@ -11241,28 +11246,28 @@
       <c r="G161" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="H161" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I161" s="30" t="s">
+      <c r="H161" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I161" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="J161" s="30" t="s">
+      <c r="J161" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="K161" s="30" t="s">
+      <c r="K161" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="L161" s="30" t="s">
+      <c r="L161" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M161" s="30" t="s">
+      <c r="M161" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="N161" s="30" t="s">
+      <c r="N161" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="O161" s="30" t="s">
+      <c r="O161" s="31" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11273,7 +11278,7 @@
       <c r="B162" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="29" t="n">
+      <c r="C162" s="30" t="n">
         <v>0.049</v>
       </c>
       <c r="D162" s="29"/>
@@ -11282,18 +11287,18 @@
       <c r="G162" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H162" s="30" t="s">
+      <c r="H162" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I162" s="30"/>
-      <c r="J162" s="30"/>
-      <c r="K162" s="30"/>
-      <c r="L162" s="30"/>
-      <c r="M162" s="30"/>
-      <c r="N162" s="30" t="s">
+      <c r="I162" s="31"/>
+      <c r="J162" s="31"/>
+      <c r="K162" s="31"/>
+      <c r="L162" s="31"/>
+      <c r="M162" s="31"/>
+      <c r="N162" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O162" s="30"/>
+      <c r="O162" s="31"/>
     </row>
     <row r="163" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="29" t="s">
@@ -11302,7 +11307,7 @@
       <c r="B163" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C163" s="29" t="n">
+      <c r="C163" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D163" s="29"/>
@@ -11311,18 +11316,18 @@
       <c r="G163" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H163" s="30" t="s">
+      <c r="H163" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="I163" s="30"/>
-      <c r="J163" s="30"/>
-      <c r="K163" s="30"/>
-      <c r="L163" s="30"/>
-      <c r="M163" s="30"/>
-      <c r="N163" s="30" t="s">
+      <c r="I163" s="31"/>
+      <c r="J163" s="31"/>
+      <c r="K163" s="31"/>
+      <c r="L163" s="31"/>
+      <c r="M163" s="31"/>
+      <c r="N163" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O163" s="30"/>
+      <c r="O163" s="31"/>
     </row>
     <row r="164" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="29" t="s">
@@ -11338,18 +11343,18 @@
       <c r="G164" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H164" s="30" t="s">
+      <c r="H164" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="I164" s="30"/>
-      <c r="J164" s="30"/>
-      <c r="K164" s="30"/>
-      <c r="L164" s="30"/>
-      <c r="M164" s="30"/>
-      <c r="N164" s="30" t="s">
+      <c r="I164" s="31"/>
+      <c r="J164" s="31"/>
+      <c r="K164" s="31"/>
+      <c r="L164" s="31"/>
+      <c r="M164" s="31"/>
+      <c r="N164" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O164" s="30"/>
+      <c r="O164" s="31"/>
     </row>
     <row r="165" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="29" t="s">
@@ -11358,7 +11363,7 @@
       <c r="B165" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C165" s="29" t="n">
+      <c r="C165" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D165" s="29"/>
@@ -11367,18 +11372,18 @@
       <c r="G165" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H165" s="30" t="s">
+      <c r="H165" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="I165" s="30"/>
-      <c r="J165" s="30"/>
-      <c r="K165" s="30"/>
-      <c r="L165" s="30"/>
-      <c r="M165" s="30"/>
-      <c r="N165" s="30" t="s">
+      <c r="I165" s="31"/>
+      <c r="J165" s="31"/>
+      <c r="K165" s="31"/>
+      <c r="L165" s="31"/>
+      <c r="M165" s="31"/>
+      <c r="N165" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O165" s="30"/>
+      <c r="O165" s="31"/>
     </row>
     <row r="166" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="29" t="s">
@@ -11394,18 +11399,18 @@
       <c r="G166" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H166" s="30" t="s">
+      <c r="H166" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="I166" s="30"/>
-      <c r="J166" s="30"/>
-      <c r="K166" s="30"/>
-      <c r="L166" s="30"/>
-      <c r="M166" s="30"/>
-      <c r="N166" s="30" t="s">
+      <c r="I166" s="31"/>
+      <c r="J166" s="31"/>
+      <c r="K166" s="31"/>
+      <c r="L166" s="31"/>
+      <c r="M166" s="31"/>
+      <c r="N166" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O166" s="30"/>
+      <c r="O166" s="31"/>
     </row>
     <row r="167" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="29" t="s">
@@ -11414,7 +11419,7 @@
       <c r="B167" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="C167" s="29" t="n">
+      <c r="C167" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D167" s="29"/>
@@ -11423,18 +11428,18 @@
       <c r="G167" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H167" s="30" t="s">
+      <c r="H167" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="I167" s="30"/>
-      <c r="J167" s="30"/>
-      <c r="K167" s="30"/>
-      <c r="L167" s="30"/>
-      <c r="M167" s="30"/>
-      <c r="N167" s="30" t="s">
+      <c r="I167" s="31"/>
+      <c r="J167" s="31"/>
+      <c r="K167" s="31"/>
+      <c r="L167" s="31"/>
+      <c r="M167" s="31"/>
+      <c r="N167" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O167" s="30"/>
+      <c r="O167" s="31"/>
     </row>
     <row r="168" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="29" t="s">
@@ -11450,18 +11455,18 @@
       <c r="G168" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H168" s="30" t="s">
+      <c r="H168" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="I168" s="30"/>
-      <c r="J168" s="30"/>
-      <c r="K168" s="30"/>
-      <c r="L168" s="30"/>
-      <c r="M168" s="30"/>
-      <c r="N168" s="30" t="s">
+      <c r="I168" s="31"/>
+      <c r="J168" s="31"/>
+      <c r="K168" s="31"/>
+      <c r="L168" s="31"/>
+      <c r="M168" s="31"/>
+      <c r="N168" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O168" s="30"/>
+      <c r="O168" s="31"/>
     </row>
     <row r="169" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="29" t="s">
@@ -11470,7 +11475,7 @@
       <c r="B169" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="C169" s="29" t="n">
+      <c r="C169" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D169" s="29"/>
@@ -11479,18 +11484,18 @@
       <c r="G169" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H169" s="30" t="s">
+      <c r="H169" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="I169" s="30"/>
-      <c r="J169" s="30"/>
-      <c r="K169" s="30"/>
-      <c r="L169" s="30"/>
-      <c r="M169" s="30"/>
-      <c r="N169" s="30" t="s">
+      <c r="I169" s="31"/>
+      <c r="J169" s="31"/>
+      <c r="K169" s="31"/>
+      <c r="L169" s="31"/>
+      <c r="M169" s="31"/>
+      <c r="N169" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O169" s="30"/>
+      <c r="O169" s="31"/>
     </row>
     <row r="170" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="29" t="s">
@@ -11499,7 +11504,7 @@
       <c r="B170" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="C170" s="29" t="n">
+      <c r="C170" s="30" t="n">
         <v>9.81981226707526</v>
       </c>
       <c r="D170" s="29"/>
@@ -11508,18 +11513,18 @@
       <c r="G170" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H170" s="30" t="s">
+      <c r="H170" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I170" s="30"/>
-      <c r="J170" s="30"/>
-      <c r="K170" s="30"/>
-      <c r="L170" s="30"/>
-      <c r="M170" s="30"/>
-      <c r="N170" s="30" t="s">
+      <c r="I170" s="31"/>
+      <c r="J170" s="31"/>
+      <c r="K170" s="31"/>
+      <c r="L170" s="31"/>
+      <c r="M170" s="31"/>
+      <c r="N170" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O170" s="30"/>
+      <c r="O170" s="31"/>
     </row>
     <row r="171" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="29" t="s">
@@ -11528,7 +11533,7 @@
       <c r="B171" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="C171" s="29" t="n">
+      <c r="C171" s="30" t="n">
         <v>8.75261897833421</v>
       </c>
       <c r="D171" s="29"/>
@@ -11537,18 +11542,18 @@
       <c r="G171" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H171" s="30" t="s">
+      <c r="H171" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="I171" s="30"/>
-      <c r="J171" s="30"/>
-      <c r="K171" s="30"/>
-      <c r="L171" s="30"/>
-      <c r="M171" s="30"/>
-      <c r="N171" s="30" t="s">
+      <c r="I171" s="31"/>
+      <c r="J171" s="31"/>
+      <c r="K171" s="31"/>
+      <c r="L171" s="31"/>
+      <c r="M171" s="31"/>
+      <c r="N171" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O171" s="30"/>
+      <c r="O171" s="31"/>
     </row>
     <row r="172" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="29" t="s">
@@ -11557,7 +11562,7 @@
       <c r="B172" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="C172" s="29" t="n">
+      <c r="C172" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D172" s="29"/>
@@ -11566,18 +11571,18 @@
       <c r="G172" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H172" s="30" t="s">
+      <c r="H172" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I172" s="30"/>
-      <c r="J172" s="30"/>
-      <c r="K172" s="30"/>
-      <c r="L172" s="30"/>
-      <c r="M172" s="30"/>
-      <c r="N172" s="30" t="s">
+      <c r="I172" s="31"/>
+      <c r="J172" s="31"/>
+      <c r="K172" s="31"/>
+      <c r="L172" s="31"/>
+      <c r="M172" s="31"/>
+      <c r="N172" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O172" s="30"/>
+      <c r="O172" s="31"/>
     </row>
     <row r="173" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="29" t="s">
@@ -11595,18 +11600,18 @@
       <c r="G173" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H173" s="30" t="s">
+      <c r="H173" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="I173" s="30"/>
-      <c r="J173" s="30"/>
-      <c r="K173" s="30"/>
-      <c r="L173" s="30"/>
-      <c r="M173" s="30"/>
-      <c r="N173" s="30" t="s">
+      <c r="I173" s="31"/>
+      <c r="J173" s="31"/>
+      <c r="K173" s="31"/>
+      <c r="L173" s="31"/>
+      <c r="M173" s="31"/>
+      <c r="N173" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O173" s="30"/>
+      <c r="O173" s="31"/>
     </row>
     <row r="174" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="29" t="s">
@@ -11615,7 +11620,7 @@
       <c r="B174" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="C174" s="29" t="n">
+      <c r="C174" s="30" t="n">
         <v>0.0781990521327014</v>
       </c>
       <c r="D174" s="29"/>
@@ -11624,18 +11629,18 @@
       <c r="G174" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H174" s="30" t="s">
+      <c r="H174" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="I174" s="30"/>
-      <c r="J174" s="30"/>
-      <c r="K174" s="30"/>
-      <c r="L174" s="30"/>
-      <c r="M174" s="30"/>
-      <c r="N174" s="30" t="s">
+      <c r="I174" s="31"/>
+      <c r="J174" s="31"/>
+      <c r="K174" s="31"/>
+      <c r="L174" s="31"/>
+      <c r="M174" s="31"/>
+      <c r="N174" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O174" s="30"/>
+      <c r="O174" s="31"/>
     </row>
     <row r="175" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="29" t="s">
@@ -11644,7 +11649,7 @@
       <c r="B175" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="C175" s="29" t="n">
+      <c r="C175" s="30" t="n">
         <v>0.976890656063618</v>
       </c>
       <c r="D175" s="29"/>
@@ -11653,18 +11658,18 @@
       <c r="G175" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H175" s="30" t="s">
+      <c r="H175" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="I175" s="30"/>
-      <c r="J175" s="30"/>
-      <c r="K175" s="30"/>
-      <c r="L175" s="30"/>
-      <c r="M175" s="30"/>
-      <c r="N175" s="30" t="s">
+      <c r="I175" s="31"/>
+      <c r="J175" s="31"/>
+      <c r="K175" s="31"/>
+      <c r="L175" s="31"/>
+      <c r="M175" s="31"/>
+      <c r="N175" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O175" s="30"/>
+      <c r="O175" s="31"/>
     </row>
     <row r="176" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="29" t="s">
@@ -11673,7 +11678,7 @@
       <c r="B176" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="C176" s="29" t="n">
+      <c r="C176" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D176" s="29"/>
@@ -11682,18 +11687,18 @@
       <c r="G176" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H176" s="30" t="s">
+      <c r="H176" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="I176" s="30"/>
-      <c r="J176" s="30"/>
-      <c r="K176" s="30"/>
-      <c r="L176" s="30"/>
-      <c r="M176" s="30"/>
-      <c r="N176" s="30" t="s">
+      <c r="I176" s="31"/>
+      <c r="J176" s="31"/>
+      <c r="K176" s="31"/>
+      <c r="L176" s="31"/>
+      <c r="M176" s="31"/>
+      <c r="N176" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O176" s="30"/>
+      <c r="O176" s="31"/>
     </row>
     <row r="177" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="29" t="s">
@@ -11702,7 +11707,7 @@
       <c r="B177" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="C177" s="29" t="n">
+      <c r="C177" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D177" s="29"/>
@@ -11711,18 +11716,18 @@
       <c r="G177" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H177" s="30" t="s">
+      <c r="H177" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I177" s="30"/>
-      <c r="J177" s="30"/>
-      <c r="K177" s="30"/>
-      <c r="L177" s="30"/>
-      <c r="M177" s="30"/>
-      <c r="N177" s="30" t="s">
+      <c r="I177" s="31"/>
+      <c r="J177" s="31"/>
+      <c r="K177" s="31"/>
+      <c r="L177" s="31"/>
+      <c r="M177" s="31"/>
+      <c r="N177" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O177" s="30"/>
+      <c r="O177" s="31"/>
     </row>
     <row r="178" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="29" t="s">
@@ -11731,7 +11736,7 @@
       <c r="B178" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="C178" s="29" t="n">
+      <c r="C178" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D178" s="29"/>
@@ -11740,18 +11745,18 @@
       <c r="G178" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H178" s="30" t="s">
+      <c r="H178" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="I178" s="30"/>
-      <c r="J178" s="30"/>
-      <c r="K178" s="30"/>
-      <c r="L178" s="30"/>
-      <c r="M178" s="30"/>
-      <c r="N178" s="30" t="s">
+      <c r="I178" s="31"/>
+      <c r="J178" s="31"/>
+      <c r="K178" s="31"/>
+      <c r="L178" s="31"/>
+      <c r="M178" s="31"/>
+      <c r="N178" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O178" s="30"/>
+      <c r="O178" s="31"/>
     </row>
     <row r="179" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="29" t="s">
@@ -11760,7 +11765,7 @@
       <c r="B179" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="C179" s="29" t="n">
+      <c r="C179" s="30" t="n">
         <v>0.162009749681374</v>
       </c>
       <c r="D179" s="29"/>
@@ -11769,18 +11774,18 @@
       <c r="G179" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H179" s="30" t="s">
+      <c r="H179" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="I179" s="30"/>
-      <c r="J179" s="30"/>
-      <c r="K179" s="30"/>
-      <c r="L179" s="30"/>
-      <c r="M179" s="30"/>
-      <c r="N179" s="30" t="s">
+      <c r="I179" s="31"/>
+      <c r="J179" s="31"/>
+      <c r="K179" s="31"/>
+      <c r="L179" s="31"/>
+      <c r="M179" s="31"/>
+      <c r="N179" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O179" s="30"/>
+      <c r="O179" s="31"/>
     </row>
     <row r="180" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="29" t="s">
@@ -11789,7 +11794,7 @@
       <c r="B180" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="C180" s="29" t="n">
+      <c r="C180" s="30" t="n">
         <v>0.025</v>
       </c>
       <c r="D180" s="29"/>
@@ -11798,18 +11803,18 @@
       <c r="G180" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H180" s="30" t="s">
+      <c r="H180" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I180" s="30"/>
-      <c r="J180" s="30"/>
-      <c r="K180" s="30"/>
-      <c r="L180" s="30"/>
-      <c r="M180" s="30"/>
-      <c r="N180" s="30" t="s">
+      <c r="I180" s="31"/>
+      <c r="J180" s="31"/>
+      <c r="K180" s="31"/>
+      <c r="L180" s="31"/>
+      <c r="M180" s="31"/>
+      <c r="N180" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O180" s="30"/>
+      <c r="O180" s="31"/>
     </row>
     <row r="181" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="29" t="s">
@@ -11818,7 +11823,7 @@
       <c r="B181" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="C181" s="29" t="n">
+      <c r="C181" s="30" t="n">
         <v>1107600000</v>
       </c>
       <c r="D181" s="29"/>
@@ -11827,18 +11832,18 @@
       <c r="G181" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H181" s="30" t="s">
+      <c r="H181" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="I181" s="30"/>
-      <c r="J181" s="30"/>
-      <c r="K181" s="30"/>
-      <c r="L181" s="30"/>
-      <c r="M181" s="30"/>
-      <c r="N181" s="30" t="s">
+      <c r="I181" s="31"/>
+      <c r="J181" s="31"/>
+      <c r="K181" s="31"/>
+      <c r="L181" s="31"/>
+      <c r="M181" s="31"/>
+      <c r="N181" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O181" s="30"/>
+      <c r="O181" s="31"/>
     </row>
     <row r="182" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="29" t="s">
@@ -11847,7 +11852,7 @@
       <c r="B182" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="C182" s="29" t="n">
+      <c r="C182" s="30" t="n">
         <v>8.88</v>
       </c>
       <c r="D182" s="29"/>
@@ -11856,18 +11861,18 @@
       <c r="G182" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H182" s="30" t="s">
+      <c r="H182" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="I182" s="30"/>
-      <c r="J182" s="30"/>
-      <c r="K182" s="30"/>
-      <c r="L182" s="30"/>
-      <c r="M182" s="30"/>
-      <c r="N182" s="30" t="s">
+      <c r="I182" s="31"/>
+      <c r="J182" s="31"/>
+      <c r="K182" s="31"/>
+      <c r="L182" s="31"/>
+      <c r="M182" s="31"/>
+      <c r="N182" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O182" s="30"/>
+      <c r="O182" s="31"/>
     </row>
     <row r="183" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="29" t="s">
@@ -11876,7 +11881,7 @@
       <c r="B183" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C183" s="29" t="n">
+      <c r="C183" s="30" t="n">
         <v>2033000000</v>
       </c>
       <c r="D183" s="29"/>
@@ -11885,18 +11890,18 @@
       <c r="G183" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H183" s="30" t="s">
+      <c r="H183" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="I183" s="30"/>
-      <c r="J183" s="30"/>
-      <c r="K183" s="30"/>
-      <c r="L183" s="30"/>
-      <c r="M183" s="30"/>
-      <c r="N183" s="30" t="s">
+      <c r="I183" s="31"/>
+      <c r="J183" s="31"/>
+      <c r="K183" s="31"/>
+      <c r="L183" s="31"/>
+      <c r="M183" s="31"/>
+      <c r="N183" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O183" s="30"/>
+      <c r="O183" s="31"/>
     </row>
     <row r="184" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="29" t="s">
@@ -11905,7 +11910,7 @@
       <c r="B184" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="C184" s="29" t="n">
+      <c r="C184" s="30" t="n">
         <v>8.79</v>
       </c>
       <c r="D184" s="29"/>
@@ -11914,18 +11919,18 @@
       <c r="G184" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="H184" s="30" t="s">
+      <c r="H184" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="I184" s="30"/>
-      <c r="J184" s="30"/>
-      <c r="K184" s="30"/>
-      <c r="L184" s="30"/>
-      <c r="M184" s="30"/>
-      <c r="N184" s="30" t="s">
+      <c r="I184" s="31"/>
+      <c r="J184" s="31"/>
+      <c r="K184" s="31"/>
+      <c r="L184" s="31"/>
+      <c r="M184" s="31"/>
+      <c r="N184" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="O184" s="30"/>
+      <c r="O184" s="31"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O184"/>
